--- a/research/traditional_assets/database/data/kenya/kenya_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_farming_agriculture.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1302341477772479</v>
+        <v>0.1298749453339161</v>
       </c>
       <c r="C2">
-        <v>2.98</v>
+        <v>2.962931774928635</v>
       </c>
       <c r="D2">
-        <v>2.98</v>
+        <v>2.992731774928635</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.0298</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0298</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1573,28 +1573,28 @@
         <v>0.121</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00149894</v>
       </c>
       <c r="N2">
-        <v>0.121</v>
+        <v>0.11950106</v>
       </c>
       <c r="O2">
-        <v>0.0363</v>
+        <v>0.035850318</v>
       </c>
       <c r="P2">
-        <v>0.0847</v>
+        <v>0.083650742</v>
       </c>
       <c r="Q2">
-        <v>0.1897</v>
+        <v>0.188650742</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1302341477772479</v>
+        <v>0.1308311569029456</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5928748568778965</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>80.72371142273873</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1298749453339161</v>
+        <v>0.1295157428905844</v>
       </c>
       <c r="C3">
-        <v>2.962931774928635</v>
+        <v>2.945972807316006</v>
       </c>
       <c r="D3">
-        <v>2.992731774928635</v>
+        <v>3.005572807316006</v>
       </c>
       <c r="E3">
-        <v>0.0298</v>
+        <v>0.0596</v>
       </c>
       <c r="F3">
-        <v>0.0298</v>
+        <v>0.0596</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1655,28 +1655,28 @@
         <v>0.121</v>
       </c>
       <c r="M3">
-        <v>0.00149894</v>
+        <v>0.00299788</v>
       </c>
       <c r="N3">
-        <v>0.11950106</v>
+        <v>0.11800212</v>
       </c>
       <c r="O3">
-        <v>0.035850318</v>
+        <v>0.035400636</v>
       </c>
       <c r="P3">
-        <v>0.083650742</v>
+        <v>0.082601484</v>
       </c>
       <c r="Q3">
-        <v>0.188650742</v>
+        <v>0.187601484</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1308311569029456</v>
+        <v>0.1314403498883514</v>
       </c>
       <c r="T3">
-        <v>0.5928748568778965</v>
+        <v>0.5971224199734539</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>80.72371142273873</v>
+        <v>40.36185571136937</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1295157428905844</v>
+        <v>0.1291565404472526</v>
       </c>
       <c r="C4">
-        <v>2.945972807316006</v>
+        <v>2.929124509608431</v>
       </c>
       <c r="D4">
-        <v>3.005572807316006</v>
+        <v>3.018524509608431</v>
       </c>
       <c r="E4">
-        <v>0.0596</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="F4">
-        <v>0.0596</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1737,28 +1737,28 @@
         <v>0.121</v>
       </c>
       <c r="M4">
-        <v>0.00299788</v>
+        <v>0.004496819999999999</v>
       </c>
       <c r="N4">
-        <v>0.11800212</v>
+        <v>0.11650318</v>
       </c>
       <c r="O4">
-        <v>0.035400636</v>
+        <v>0.034950954</v>
       </c>
       <c r="P4">
-        <v>0.082601484</v>
+        <v>0.08155222600000001</v>
       </c>
       <c r="Q4">
-        <v>0.187601484</v>
+        <v>0.186552226</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1314403498883514</v>
+        <v>0.1320621035538687</v>
       </c>
       <c r="T4">
-        <v>0.5971224199734539</v>
+        <v>0.6014575616895382</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>40.36185571136937</v>
+        <v>26.90790380757958</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1291565404472526</v>
+        <v>0.1287973380039209</v>
       </c>
       <c r="C5">
-        <v>2.929124509608431</v>
+        <v>2.912388318703813</v>
       </c>
       <c r="D5">
-        <v>3.018524509608431</v>
+        <v>3.031588318703813</v>
       </c>
       <c r="E5">
-        <v>0.08939999999999999</v>
+        <v>0.1192</v>
       </c>
       <c r="F5">
-        <v>0.08939999999999999</v>
+        <v>0.1192</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1819,28 +1819,28 @@
         <v>0.121</v>
       </c>
       <c r="M5">
-        <v>0.004496819999999999</v>
+        <v>0.00599576</v>
       </c>
       <c r="N5">
-        <v>0.11650318</v>
+        <v>0.11500424</v>
       </c>
       <c r="O5">
-        <v>0.034950954</v>
+        <v>0.034501272</v>
       </c>
       <c r="P5">
-        <v>0.08155222600000001</v>
+        <v>0.08050296799999999</v>
       </c>
       <c r="Q5">
-        <v>0.186552226</v>
+        <v>0.185502968</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1320621035538687</v>
+        <v>0.1326968104207509</v>
       </c>
       <c r="T5">
-        <v>0.6014575616895382</v>
+        <v>0.605883018858041</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>26.90790380757958</v>
+        <v>20.18092785568468</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1287973380039209</v>
+        <v>0.1284381355605891</v>
       </c>
       <c r="C6">
-        <v>2.912388318703813</v>
+        <v>2.89576569648306</v>
       </c>
       <c r="D6">
-        <v>3.031588318703813</v>
+        <v>3.044765696483061</v>
       </c>
       <c r="E6">
-        <v>0.1192</v>
+        <v>0.149</v>
       </c>
       <c r="F6">
-        <v>0.1192</v>
+        <v>0.149</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1901,28 +1901,28 @@
         <v>0.121</v>
       </c>
       <c r="M6">
-        <v>0.00599576</v>
+        <v>0.007494699999999999</v>
       </c>
       <c r="N6">
-        <v>0.11500424</v>
+        <v>0.1135053</v>
       </c>
       <c r="O6">
-        <v>0.034501272</v>
+        <v>0.03405159</v>
       </c>
       <c r="P6">
-        <v>0.08050296799999999</v>
+        <v>0.07945371000000001</v>
       </c>
       <c r="Q6">
-        <v>0.185502968</v>
+        <v>0.18445371</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1326968104207509</v>
+        <v>0.1333448795374622</v>
       </c>
       <c r="T6">
-        <v>0.605883018858041</v>
+        <v>0.6104016435458806</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>20.18092785568468</v>
+        <v>16.14474228454775</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1284381355605891</v>
+        <v>0.1280789331172574</v>
       </c>
       <c r="C7">
-        <v>2.89576569648306</v>
+        <v>2.879258130355419</v>
       </c>
       <c r="D7">
-        <v>3.044765696483061</v>
+        <v>3.058058130355419</v>
       </c>
       <c r="E7">
-        <v>0.149</v>
+        <v>0.1788</v>
       </c>
       <c r="F7">
-        <v>0.149</v>
+        <v>0.1788</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1983,28 +1983,28 @@
         <v>0.121</v>
       </c>
       <c r="M7">
-        <v>0.007494699999999999</v>
+        <v>0.008993640000000001</v>
       </c>
       <c r="N7">
-        <v>0.1135053</v>
+        <v>0.11200636</v>
       </c>
       <c r="O7">
-        <v>0.03405159</v>
+        <v>0.033601908</v>
       </c>
       <c r="P7">
-        <v>0.07945371000000001</v>
+        <v>0.078404452</v>
       </c>
       <c r="Q7">
-        <v>0.18445371</v>
+        <v>0.183404452</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1333448795374622</v>
+        <v>0.1340067373587845</v>
       </c>
       <c r="T7">
-        <v>0.6104016435458806</v>
+        <v>0.6150164091845253</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.14474228454775</v>
+        <v>13.45395190378979</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1280789331172574</v>
+        <v>0.1277932306739257</v>
       </c>
       <c r="C8">
-        <v>2.879258130355419</v>
+        <v>2.860113823179226</v>
       </c>
       <c r="D8">
-        <v>3.058058130355419</v>
+        <v>3.068713823179226</v>
       </c>
       <c r="E8">
-        <v>0.1788</v>
+        <v>0.2086</v>
       </c>
       <c r="F8">
-        <v>0.1788</v>
+        <v>0.2086</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2065,45 +2065,45 @@
         <v>0.121</v>
       </c>
       <c r="M8">
-        <v>0.008993639999999999</v>
+        <v>0.01080548</v>
       </c>
       <c r="N8">
-        <v>0.11200636</v>
+        <v>0.11019452</v>
       </c>
       <c r="O8">
-        <v>0.033601908</v>
+        <v>0.033058356</v>
       </c>
       <c r="P8">
-        <v>0.078404452</v>
+        <v>0.07713616399999999</v>
       </c>
       <c r="Q8">
-        <v>0.183404452</v>
+        <v>0.182136164</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1340067373587845</v>
+        <v>0.1346828286816405</v>
       </c>
       <c r="T8">
-        <v>0.6150164091845253</v>
+        <v>0.6197304170949689</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.3</v>
       </c>
       <c r="W8">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.45395190378979</v>
+        <v>11.19802174452222</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1277932306739256</v>
+        <v>0.1275397282305939</v>
       </c>
       <c r="C9">
-        <v>2.860113823179227</v>
+        <v>2.839830938893965</v>
       </c>
       <c r="D9">
-        <v>3.068713823179227</v>
+        <v>3.078230938893965</v>
       </c>
       <c r="E9">
-        <v>0.2086</v>
+        <v>0.2384</v>
       </c>
       <c r="F9">
-        <v>0.2086</v>
+        <v>0.2384</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2147,45 +2147,45 @@
         <v>0.121</v>
       </c>
       <c r="M9">
-        <v>0.01080548</v>
+        <v>0.0127544</v>
       </c>
       <c r="N9">
-        <v>0.11019452</v>
+        <v>0.1082456</v>
       </c>
       <c r="O9">
-        <v>0.033058356</v>
+        <v>0.03247368</v>
       </c>
       <c r="P9">
-        <v>0.07713616399999999</v>
+        <v>0.07577191999999999</v>
       </c>
       <c r="Q9">
-        <v>0.182136164</v>
+        <v>0.18077192</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1346828286816405</v>
+        <v>0.1353736176419499</v>
       </c>
       <c r="T9">
-        <v>0.6197304170949689</v>
+        <v>0.6245469034382483</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.3</v>
       </c>
       <c r="W9">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>11.19802174452222</v>
+        <v>9.486922160195698</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1275397282305939</v>
+        <v>0.1272029257872622</v>
       </c>
       <c r="C10">
-        <v>2.839830938893965</v>
+        <v>2.822767037643884</v>
       </c>
       <c r="D10">
-        <v>3.078230938893965</v>
+        <v>3.090967037643884</v>
       </c>
       <c r="E10">
-        <v>0.2384</v>
+        <v>0.2682</v>
       </c>
       <c r="F10">
-        <v>0.2384</v>
+        <v>0.2682</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2229,28 +2229,28 @@
         <v>0.121</v>
       </c>
       <c r="M10">
-        <v>0.0127544</v>
+        <v>0.0143487</v>
       </c>
       <c r="N10">
-        <v>0.1082456</v>
+        <v>0.1066513</v>
       </c>
       <c r="O10">
-        <v>0.03247368</v>
+        <v>0.03199539</v>
       </c>
       <c r="P10">
-        <v>0.07577191999999999</v>
+        <v>0.07465591000000001</v>
       </c>
       <c r="Q10">
-        <v>0.18077192</v>
+        <v>0.17965591</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1353736176419499</v>
+        <v>0.1360795887772112</v>
       </c>
       <c r="T10">
-        <v>0.6245469034382483</v>
+        <v>0.6294692466242369</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.486922160195698</v>
+        <v>8.432819697951732</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1272029257872622</v>
+        <v>0.1269221233439304</v>
       </c>
       <c r="C11">
-        <v>2.822767037643884</v>
+        <v>2.803666351969625</v>
       </c>
       <c r="D11">
-        <v>3.090967037643884</v>
+        <v>3.101666351969625</v>
       </c>
       <c r="E11">
-        <v>0.2682</v>
+        <v>0.298</v>
       </c>
       <c r="F11">
-        <v>0.2682</v>
+        <v>0.298</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2311,45 +2311,45 @@
         <v>0.121</v>
       </c>
       <c r="M11">
-        <v>0.0143487</v>
+        <v>0.0161814</v>
       </c>
       <c r="N11">
-        <v>0.1066513</v>
+        <v>0.1048186</v>
       </c>
       <c r="O11">
-        <v>0.03199539</v>
+        <v>0.03144558</v>
       </c>
       <c r="P11">
-        <v>0.07465591000000001</v>
+        <v>0.07337302</v>
       </c>
       <c r="Q11">
-        <v>0.17965591</v>
+        <v>0.17837302</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1360795887772112</v>
+        <v>0.1368012481599227</v>
       </c>
       <c r="T11">
-        <v>0.6294692466242369</v>
+        <v>0.6345009752143587</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.3</v>
       </c>
       <c r="W11">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>8.432819697951732</v>
+        <v>7.477721334371563</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1269221233439304</v>
+        <v>0.1265909209005987</v>
       </c>
       <c r="C12">
-        <v>2.803666351969625</v>
+        <v>2.786581635602004</v>
       </c>
       <c r="D12">
-        <v>3.101666351969625</v>
+        <v>3.114381635602004</v>
       </c>
       <c r="E12">
-        <v>0.298</v>
+        <v>0.3278</v>
       </c>
       <c r="F12">
-        <v>0.298</v>
+        <v>0.3278</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2393,28 +2393,28 @@
         <v>0.121</v>
       </c>
       <c r="M12">
-        <v>0.0161814</v>
+        <v>0.01779954</v>
       </c>
       <c r="N12">
-        <v>0.1048186</v>
+        <v>0.10320046</v>
       </c>
       <c r="O12">
-        <v>0.03144558</v>
+        <v>0.030960138</v>
       </c>
       <c r="P12">
-        <v>0.07337302</v>
+        <v>0.072240322</v>
       </c>
       <c r="Q12">
-        <v>0.17837302</v>
+        <v>0.177240322</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1368012481599227</v>
+        <v>0.1375391246074142</v>
       </c>
       <c r="T12">
-        <v>0.6345009752143587</v>
+        <v>0.6396457763570675</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.477721334371563</v>
+        <v>6.79792848579233</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1265909209005987</v>
+        <v>0.1262597184572669</v>
       </c>
       <c r="C13">
-        <v>2.786581635602004</v>
+        <v>2.769601601007758</v>
       </c>
       <c r="D13">
-        <v>3.114381635602004</v>
+        <v>3.127201601007758</v>
       </c>
       <c r="E13">
-        <v>0.3278</v>
+        <v>0.3576</v>
       </c>
       <c r="F13">
-        <v>0.3278</v>
+        <v>0.3576</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2475,28 +2475,28 @@
         <v>0.121</v>
       </c>
       <c r="M13">
-        <v>0.01779954</v>
+        <v>0.01941768</v>
       </c>
       <c r="N13">
-        <v>0.10320046</v>
+        <v>0.10158232</v>
       </c>
       <c r="O13">
-        <v>0.030960138</v>
+        <v>0.030474696</v>
       </c>
       <c r="P13">
-        <v>0.072240322</v>
+        <v>0.07110762400000001</v>
       </c>
       <c r="Q13">
-        <v>0.177240322</v>
+        <v>0.176107624</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1375391246074142</v>
+        <v>0.138293770974167</v>
       </c>
       <c r="T13">
-        <v>0.6396457763570675</v>
+        <v>0.6449075047984743</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.79792848579233</v>
+        <v>6.231434445309636</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1262597184572669</v>
+        <v>0.1260195160139352</v>
       </c>
       <c r="C14">
-        <v>2.769601601007758</v>
+        <v>2.749165425456943</v>
       </c>
       <c r="D14">
-        <v>3.127201601007758</v>
+        <v>3.136565425456943</v>
       </c>
       <c r="E14">
-        <v>0.3576</v>
+        <v>0.3874</v>
       </c>
       <c r="F14">
-        <v>0.3576</v>
+        <v>0.3874</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2557,45 +2557,45 @@
         <v>0.121</v>
       </c>
       <c r="M14">
-        <v>0.01941768</v>
+        <v>0.02142322</v>
       </c>
       <c r="N14">
-        <v>0.10158232</v>
+        <v>0.09957677999999999</v>
       </c>
       <c r="O14">
-        <v>0.030474696</v>
+        <v>0.029873034</v>
       </c>
       <c r="P14">
-        <v>0.07110762400000001</v>
+        <v>0.069703746</v>
       </c>
       <c r="Q14">
-        <v>0.176107624</v>
+        <v>0.174703746</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.138293770974167</v>
+        <v>0.1390657655332588</v>
       </c>
       <c r="T14">
-        <v>0.6449075047984743</v>
+        <v>0.650290192514396</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.231434445309636</v>
+        <v>5.648077179807703</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1260195160139352</v>
+        <v>0.1256953135706034</v>
       </c>
       <c r="C15">
-        <v>2.749165425456943</v>
+        <v>2.732093107834764</v>
       </c>
       <c r="D15">
-        <v>3.136565425456943</v>
+        <v>3.149293107834764</v>
       </c>
       <c r="E15">
-        <v>0.3874</v>
+        <v>0.4172</v>
       </c>
       <c r="F15">
-        <v>0.3874</v>
+        <v>0.4172</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2639,28 +2639,28 @@
         <v>0.121</v>
       </c>
       <c r="M15">
-        <v>0.02142322</v>
+        <v>0.02307116</v>
       </c>
       <c r="N15">
-        <v>0.09957677999999999</v>
+        <v>0.09792883999999999</v>
       </c>
       <c r="O15">
-        <v>0.029873034</v>
+        <v>0.02937865199999999</v>
       </c>
       <c r="P15">
-        <v>0.069703746</v>
+        <v>0.068550188</v>
       </c>
       <c r="Q15">
-        <v>0.174703746</v>
+        <v>0.173550188</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1390657655332588</v>
+        <v>0.13985571345419</v>
       </c>
       <c r="T15">
-        <v>0.650290192514396</v>
+        <v>0.655798059014409</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.648077179807703</v>
+        <v>5.244643095535724</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1256953135706034</v>
+        <v>0.1253711111272717</v>
       </c>
       <c r="C16">
-        <v>2.732093107834764</v>
+        <v>2.715124504881548</v>
       </c>
       <c r="D16">
-        <v>3.149293107834764</v>
+        <v>3.162124504881548</v>
       </c>
       <c r="E16">
-        <v>0.4172</v>
+        <v>0.4470000000000001</v>
       </c>
       <c r="F16">
-        <v>0.4172</v>
+        <v>0.4470000000000001</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2721,28 +2721,28 @@
         <v>0.121</v>
       </c>
       <c r="M16">
-        <v>0.02307116</v>
+        <v>0.0247191</v>
       </c>
       <c r="N16">
-        <v>0.09792883999999999</v>
+        <v>0.09628089999999999</v>
       </c>
       <c r="O16">
-        <v>0.02937865199999999</v>
+        <v>0.02888427</v>
       </c>
       <c r="P16">
-        <v>0.068550188</v>
+        <v>0.06739662999999999</v>
       </c>
       <c r="Q16">
-        <v>0.173550188</v>
+        <v>0.17239663</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.13985571345419</v>
+        <v>0.1406642483850255</v>
       </c>
       <c r="T16">
-        <v>0.655798059014409</v>
+        <v>0.661435522373246</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.244643095535724</v>
+        <v>4.895000222500009</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1253711111272717</v>
+        <v>0.1250469086839399</v>
       </c>
       <c r="C17">
-        <v>2.715124504881548</v>
+        <v>2.698260889500543</v>
       </c>
       <c r="D17">
-        <v>3.162124504881548</v>
+        <v>3.175060889500543</v>
       </c>
       <c r="E17">
-        <v>0.447</v>
+        <v>0.4768</v>
       </c>
       <c r="F17">
-        <v>0.447</v>
+        <v>0.4768</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2803,28 +2803,28 @@
         <v>0.121</v>
       </c>
       <c r="M17">
-        <v>0.0247191</v>
+        <v>0.02636704</v>
       </c>
       <c r="N17">
-        <v>0.0962809</v>
+        <v>0.09463295999999999</v>
       </c>
       <c r="O17">
-        <v>0.02888427</v>
+        <v>0.028389888</v>
       </c>
       <c r="P17">
-        <v>0.06739663</v>
+        <v>0.06624307199999999</v>
       </c>
       <c r="Q17">
-        <v>0.17239663</v>
+        <v>0.171243072</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1406642483850255</v>
+        <v>0.1414920341475476</v>
       </c>
       <c r="T17">
-        <v>0.661435522373246</v>
+        <v>0.6672072110501504</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.89500022250001</v>
+        <v>4.589062708593759</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1250469086839399</v>
+        <v>0.1250202062406082</v>
       </c>
       <c r="C18">
-        <v>2.698260889500543</v>
+        <v>2.669531094786542</v>
       </c>
       <c r="D18">
-        <v>3.175060889500543</v>
+        <v>3.176131094786542</v>
       </c>
       <c r="E18">
-        <v>0.4768</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="F18">
-        <v>0.4768</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2885,45 +2885,45 @@
         <v>0.121</v>
       </c>
       <c r="M18">
-        <v>0.02636704</v>
+        <v>0.02928148000000001</v>
       </c>
       <c r="N18">
-        <v>0.09463295999999999</v>
+        <v>0.09171852</v>
       </c>
       <c r="O18">
-        <v>0.028389888</v>
+        <v>0.027515556</v>
       </c>
       <c r="P18">
-        <v>0.06624307199999999</v>
+        <v>0.064202964</v>
       </c>
       <c r="Q18">
-        <v>0.171243072</v>
+        <v>0.169202964</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1414920341475476</v>
+        <v>0.1423397665549497</v>
       </c>
       <c r="T18">
-        <v>0.6672072110501504</v>
+        <v>0.6731179765626429</v>
       </c>
       <c r="U18">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.589062708593759</v>
+        <v>4.132304787872743</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1250202062406082</v>
+        <v>0.1251545037972765</v>
       </c>
       <c r="C19">
-        <v>2.669531094786542</v>
+        <v>2.634355890793363</v>
       </c>
       <c r="D19">
-        <v>3.176131094786542</v>
+        <v>3.170755890793363</v>
       </c>
       <c r="E19">
-        <v>0.5066000000000001</v>
+        <v>0.5364000000000001</v>
       </c>
       <c r="F19">
-        <v>0.5066000000000001</v>
+        <v>0.5364000000000001</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2967,45 +2967,45 @@
         <v>0.121</v>
       </c>
       <c r="M19">
-        <v>0.02928148000000001</v>
+        <v>0.03288132000000001</v>
       </c>
       <c r="N19">
-        <v>0.09171852</v>
+        <v>0.08811867999999999</v>
       </c>
       <c r="O19">
-        <v>0.027515556</v>
+        <v>0.026435604</v>
       </c>
       <c r="P19">
-        <v>0.064202964</v>
+        <v>0.06168307599999999</v>
       </c>
       <c r="Q19">
-        <v>0.169202964</v>
+        <v>0.166683076</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1423397665549497</v>
+        <v>0.1432081753625323</v>
       </c>
       <c r="T19">
-        <v>0.6731179765626429</v>
+        <v>0.6791729070876351</v>
       </c>
       <c r="U19">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.132304787872743</v>
+        <v>3.679900928551529</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1251545037972765</v>
+        <v>0.1252447013539447</v>
       </c>
       <c r="C20">
-        <v>2.634355890793363</v>
+        <v>2.600955972494635</v>
       </c>
       <c r="D20">
-        <v>3.170755890793363</v>
+        <v>3.167155972494635</v>
       </c>
       <c r="E20">
-        <v>0.5364</v>
+        <v>0.5662</v>
       </c>
       <c r="F20">
-        <v>0.5364</v>
+        <v>0.5662</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3049,45 +3049,45 @@
         <v>0.121</v>
       </c>
       <c r="M20">
-        <v>0.03288132</v>
+        <v>0.03629342000000001</v>
       </c>
       <c r="N20">
-        <v>0.08811868</v>
+        <v>0.08470657999999999</v>
       </c>
       <c r="O20">
-        <v>0.026435604</v>
+        <v>0.025411974</v>
       </c>
       <c r="P20">
-        <v>0.061683076</v>
+        <v>0.05929460599999999</v>
       </c>
       <c r="Q20">
-        <v>0.166683076</v>
+        <v>0.164294606</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1432081753625323</v>
+        <v>0.1440980263628947</v>
       </c>
       <c r="T20">
-        <v>0.6791729070876351</v>
+        <v>0.6853773420700346</v>
       </c>
       <c r="U20">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.67990092855153</v>
+        <v>3.333937666937973</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1252447013539447</v>
+        <v>0.124982098910613</v>
       </c>
       <c r="C21">
-        <v>2.600955972494635</v>
+        <v>2.581659645777263</v>
       </c>
       <c r="D21">
-        <v>3.167155972494635</v>
+        <v>3.177659645777263</v>
       </c>
       <c r="E21">
-        <v>0.5662</v>
+        <v>0.596</v>
       </c>
       <c r="F21">
-        <v>0.5662</v>
+        <v>0.596</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3131,28 +3131,28 @@
         <v>0.121</v>
       </c>
       <c r="M21">
-        <v>0.03629342000000001</v>
+        <v>0.0382036</v>
       </c>
       <c r="N21">
-        <v>0.08470657999999999</v>
+        <v>0.08279639999999999</v>
       </c>
       <c r="O21">
-        <v>0.025411974</v>
+        <v>0.02483892</v>
       </c>
       <c r="P21">
-        <v>0.05929460599999999</v>
+        <v>0.05795747999999999</v>
       </c>
       <c r="Q21">
-        <v>0.164294606</v>
+        <v>0.16295748</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1440980263628947</v>
+        <v>0.1450101236382662</v>
       </c>
       <c r="T21">
-        <v>0.6853773420700346</v>
+        <v>0.6917368879269942</v>
       </c>
       <c r="U21">
         <v>0.0641</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.333937666937973</v>
+        <v>3.167240783591075</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.124982098910613</v>
+        <v>0.1247194964672813</v>
       </c>
       <c r="C22">
-        <v>2.581659645777263</v>
+        <v>2.562433220424989</v>
       </c>
       <c r="D22">
-        <v>3.177659645777263</v>
+        <v>3.188233220424989</v>
       </c>
       <c r="E22">
-        <v>0.596</v>
+        <v>0.6258</v>
       </c>
       <c r="F22">
-        <v>0.596</v>
+        <v>0.6258</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3213,28 +3213,28 @@
         <v>0.121</v>
       </c>
       <c r="M22">
-        <v>0.0382036</v>
+        <v>0.04011378</v>
       </c>
       <c r="N22">
-        <v>0.08279639999999999</v>
+        <v>0.08088621999999999</v>
       </c>
       <c r="O22">
-        <v>0.02483892</v>
+        <v>0.024265866</v>
       </c>
       <c r="P22">
-        <v>0.05795747999999999</v>
+        <v>0.056620354</v>
       </c>
       <c r="Q22">
-        <v>0.16295748</v>
+        <v>0.161620354</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1450101236382662</v>
+        <v>0.1459453119839003</v>
       </c>
       <c r="T22">
-        <v>0.6917368879269942</v>
+        <v>0.6982574349448893</v>
       </c>
       <c r="U22">
         <v>0.0641</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.167240783591075</v>
+        <v>3.016419793896262</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1247194964672812</v>
+        <v>0.1256580940239495</v>
       </c>
       <c r="C23">
-        <v>2.56243322042499</v>
+        <v>2.495160902216619</v>
       </c>
       <c r="D23">
-        <v>3.18823322042499</v>
+        <v>3.150760902216619</v>
       </c>
       <c r="E23">
-        <v>0.6258</v>
+        <v>0.6556</v>
       </c>
       <c r="F23">
-        <v>0.6258</v>
+        <v>0.6556</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3295,45 +3295,45 @@
         <v>0.121</v>
       </c>
       <c r="M23">
-        <v>0.04011378</v>
+        <v>0.04713764</v>
       </c>
       <c r="N23">
-        <v>0.08088621999999999</v>
+        <v>0.07386235999999999</v>
       </c>
       <c r="O23">
-        <v>0.024265866</v>
+        <v>0.022158708</v>
       </c>
       <c r="P23">
-        <v>0.056620354</v>
+        <v>0.05170365199999999</v>
       </c>
       <c r="Q23">
-        <v>0.161620354</v>
+        <v>0.156703652</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1459453119839003</v>
+        <v>0.146904479517884</v>
       </c>
       <c r="T23">
-        <v>0.6982574349448892</v>
+        <v>0.7049451754760638</v>
       </c>
       <c r="U23">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.016419793896262</v>
+        <v>2.566950742548842</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1256580940239495</v>
+        <v>0.1260779915806177</v>
       </c>
       <c r="C24">
-        <v>2.495160902216619</v>
+        <v>2.448880709097213</v>
       </c>
       <c r="D24">
-        <v>3.150760902216619</v>
+        <v>3.134280709097213</v>
       </c>
       <c r="E24">
-        <v>0.6556</v>
+        <v>0.6854</v>
       </c>
       <c r="F24">
-        <v>0.6556</v>
+        <v>0.6854</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3377,45 +3377,45 @@
         <v>0.121</v>
       </c>
       <c r="M24">
-        <v>0.04713764</v>
+        <v>0.05195332</v>
       </c>
       <c r="N24">
-        <v>0.07386235999999999</v>
+        <v>0.06904668</v>
       </c>
       <c r="O24">
-        <v>0.022158708</v>
+        <v>0.020714004</v>
       </c>
       <c r="P24">
-        <v>0.05170365199999999</v>
+        <v>0.048332676</v>
       </c>
       <c r="Q24">
-        <v>0.156703652</v>
+        <v>0.153332676</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.146904479517884</v>
+        <v>0.1478885604943088</v>
       </c>
       <c r="T24">
-        <v>0.7049451754760638</v>
+        <v>0.7118066235535027</v>
       </c>
       <c r="U24">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.566950742548842</v>
+        <v>2.32901381470905</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1260779915806177</v>
+        <v>0.125897289137286</v>
       </c>
       <c r="C25">
-        <v>2.448880709097213</v>
+        <v>2.426151762166819</v>
       </c>
       <c r="D25">
-        <v>3.134280709097213</v>
+        <v>3.141351762166819</v>
       </c>
       <c r="E25">
-        <v>0.6854</v>
+        <v>0.7152000000000001</v>
       </c>
       <c r="F25">
-        <v>0.6854</v>
+        <v>0.7152000000000001</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3459,28 +3459,28 @@
         <v>0.121</v>
       </c>
       <c r="M25">
-        <v>0.05195332</v>
+        <v>0.05421216000000001</v>
       </c>
       <c r="N25">
-        <v>0.06904668</v>
+        <v>0.06678783999999999</v>
       </c>
       <c r="O25">
-        <v>0.020714004</v>
+        <v>0.020036352</v>
       </c>
       <c r="P25">
-        <v>0.048332676</v>
+        <v>0.04675148799999999</v>
       </c>
       <c r="Q25">
-        <v>0.153332676</v>
+        <v>0.151751488</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1478885604943088</v>
+        <v>0.1488985383385342</v>
       </c>
       <c r="T25">
-        <v>0.7118066235535027</v>
+        <v>0.718848636054032</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.32901381470905</v>
+        <v>2.231971572429506</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.125897289137286</v>
+        <v>0.1257165866939543</v>
       </c>
       <c r="C26">
-        <v>2.426151762166819</v>
+        <v>2.403454792492198</v>
       </c>
       <c r="D26">
-        <v>3.141351762166819</v>
+        <v>3.148454792492198</v>
       </c>
       <c r="E26">
-        <v>0.7151999999999999</v>
+        <v>0.745</v>
       </c>
       <c r="F26">
-        <v>0.7151999999999999</v>
+        <v>0.745</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3541,28 +3541,28 @@
         <v>0.121</v>
       </c>
       <c r="M26">
-        <v>0.05421216</v>
+        <v>0.05647100000000001</v>
       </c>
       <c r="N26">
-        <v>0.06678783999999999</v>
+        <v>0.06452899999999999</v>
       </c>
       <c r="O26">
-        <v>0.020036352</v>
+        <v>0.0193587</v>
       </c>
       <c r="P26">
-        <v>0.04675148799999999</v>
+        <v>0.0451703</v>
       </c>
       <c r="Q26">
-        <v>0.151751488</v>
+        <v>0.1501703</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1488985383385342</v>
+        <v>0.1499354489252724</v>
       </c>
       <c r="T26">
-        <v>0.718848636054032</v>
+        <v>0.7260784355545755</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.231971572429506</v>
+        <v>2.142692709532326</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1257165866939543</v>
+        <v>0.1255358842506225</v>
       </c>
       <c r="C27">
-        <v>2.403454792492198</v>
+        <v>2.380790017479919</v>
       </c>
       <c r="D27">
-        <v>3.148454792492198</v>
+        <v>3.155590017479919</v>
       </c>
       <c r="E27">
-        <v>0.745</v>
+        <v>0.7748</v>
       </c>
       <c r="F27">
-        <v>0.745</v>
+        <v>0.7748</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3623,28 +3623,28 @@
         <v>0.121</v>
       </c>
       <c r="M27">
-        <v>0.05647100000000001</v>
+        <v>0.05872984000000001</v>
       </c>
       <c r="N27">
-        <v>0.06452899999999999</v>
+        <v>0.06227015999999999</v>
       </c>
       <c r="O27">
-        <v>0.0193587</v>
+        <v>0.018681048</v>
       </c>
       <c r="P27">
-        <v>0.0451703</v>
+        <v>0.043589112</v>
       </c>
       <c r="Q27">
-        <v>0.1501703</v>
+        <v>0.148589112</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1499354489252724</v>
+        <v>0.1510003841224629</v>
       </c>
       <c r="T27">
-        <v>0.7260784355545755</v>
+        <v>0.73350363504162</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.142692709532326</v>
+        <v>2.06028145147339</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1255358842506225</v>
+        <v>0.1280389818072908</v>
       </c>
       <c r="C28">
-        <v>2.380790017479919</v>
+        <v>2.25494372058984</v>
       </c>
       <c r="D28">
-        <v>3.155590017479919</v>
+        <v>3.05954372058984</v>
       </c>
       <c r="E28">
-        <v>0.7748</v>
+        <v>0.8046000000000001</v>
       </c>
       <c r="F28">
-        <v>0.7748</v>
+        <v>0.8046000000000001</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3705,45 +3705,45 @@
         <v>0.121</v>
       </c>
       <c r="M28">
-        <v>0.05872984000000001</v>
+        <v>0.07241400000000001</v>
       </c>
       <c r="N28">
-        <v>0.06227015999999999</v>
+        <v>0.04858599999999999</v>
       </c>
       <c r="O28">
-        <v>0.018681048</v>
+        <v>0.0145758</v>
       </c>
       <c r="P28">
-        <v>0.043589112</v>
+        <v>0.03401019999999999</v>
       </c>
       <c r="Q28">
-        <v>0.148589112</v>
+        <v>0.1390102</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1510003841224629</v>
+        <v>0.1520944956264257</v>
       </c>
       <c r="T28">
-        <v>0.73350363504162</v>
+        <v>0.7411322646515974</v>
       </c>
       <c r="U28">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.06028145147339</v>
+        <v>1.670947606816361</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1280389818072908</v>
+        <v>0.127957679363959</v>
       </c>
       <c r="C29">
-        <v>2.25494372058984</v>
+        <v>2.228171415406564</v>
       </c>
       <c r="D29">
-        <v>3.05954372058984</v>
+        <v>3.062571415406564</v>
       </c>
       <c r="E29">
-        <v>0.8046000000000001</v>
+        <v>0.8344</v>
       </c>
       <c r="F29">
-        <v>0.8046000000000001</v>
+        <v>0.8344</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3787,28 +3787,28 @@
         <v>0.121</v>
       </c>
       <c r="M29">
-        <v>0.07241400000000001</v>
+        <v>0.075096</v>
       </c>
       <c r="N29">
-        <v>0.04858599999999999</v>
+        <v>0.045904</v>
       </c>
       <c r="O29">
-        <v>0.0145758</v>
+        <v>0.0137712</v>
       </c>
       <c r="P29">
-        <v>0.03401019999999999</v>
+        <v>0.0321328</v>
       </c>
       <c r="Q29">
-        <v>0.1390102</v>
+        <v>0.1371328</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1520944956264257</v>
+        <v>0.1532189991166098</v>
       </c>
       <c r="T29">
-        <v>0.7411322646515974</v>
+        <v>0.7489728006396296</v>
       </c>
       <c r="U29">
         <v>0.09</v>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.670947606816361</v>
+        <v>1.61127090657292</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.127957679363959</v>
+        <v>0.1278763769206273</v>
       </c>
       <c r="C30">
-        <v>2.228171415406564</v>
+        <v>2.201405108514036</v>
       </c>
       <c r="D30">
-        <v>3.062571415406564</v>
+        <v>3.065605108514037</v>
       </c>
       <c r="E30">
-        <v>0.8344</v>
+        <v>0.8642000000000001</v>
       </c>
       <c r="F30">
-        <v>0.8344</v>
+        <v>0.8642000000000001</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3869,28 +3869,28 @@
         <v>0.121</v>
       </c>
       <c r="M30">
-        <v>0.075096</v>
+        <v>0.077778</v>
       </c>
       <c r="N30">
-        <v>0.045904</v>
+        <v>0.043222</v>
       </c>
       <c r="O30">
-        <v>0.0137712</v>
+        <v>0.0129666</v>
       </c>
       <c r="P30">
-        <v>0.0321328</v>
+        <v>0.0302554</v>
       </c>
       <c r="Q30">
-        <v>0.1371328</v>
+        <v>0.1352554</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1532189991166098</v>
+        <v>0.1543751787614469</v>
       </c>
       <c r="T30">
-        <v>0.7489728006396296</v>
+        <v>0.7570341967963389</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.61127090657292</v>
+        <v>1.555709840829026</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1278763769206273</v>
+        <v>0.1277950744772955</v>
       </c>
       <c r="C31">
-        <v>2.201405108514037</v>
+        <v>2.174644817755127</v>
       </c>
       <c r="D31">
-        <v>3.065605108514037</v>
+        <v>3.068644817755127</v>
       </c>
       <c r="E31">
-        <v>0.8642</v>
+        <v>0.894</v>
       </c>
       <c r="F31">
-        <v>0.8642</v>
+        <v>0.894</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3951,28 +3951,28 @@
         <v>0.121</v>
       </c>
       <c r="M31">
-        <v>0.077778</v>
+        <v>0.08046</v>
       </c>
       <c r="N31">
-        <v>0.043222</v>
+        <v>0.04053999999999999</v>
       </c>
       <c r="O31">
-        <v>0.0129666</v>
+        <v>0.012162</v>
       </c>
       <c r="P31">
-        <v>0.0302554</v>
+        <v>0.02837799999999999</v>
       </c>
       <c r="Q31">
-        <v>0.1352554</v>
+        <v>0.133378</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1543751787614469</v>
+        <v>0.1555643921104222</v>
       </c>
       <c r="T31">
-        <v>0.7570341967963389</v>
+        <v>0.7653259185575255</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.555709840829026</v>
+        <v>1.503852846134725</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1277950744772955</v>
+        <v>0.1423567413522298</v>
       </c>
       <c r="C32">
-        <v>2.174644817755127</v>
+        <v>1.682064249895672</v>
       </c>
       <c r="D32">
-        <v>3.068644817755127</v>
+        <v>2.605864249895672</v>
       </c>
       <c r="E32">
-        <v>0.894</v>
+        <v>0.9238</v>
       </c>
       <c r="F32">
-        <v>0.894</v>
+        <v>0.9238</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4033,45 +4033,45 @@
         <v>0.121</v>
       </c>
       <c r="M32">
-        <v>0.08046</v>
+        <v>0.13561384</v>
       </c>
       <c r="N32">
-        <v>0.04053999999999999</v>
+        <v>-0.01461384000000002</v>
       </c>
       <c r="O32">
-        <v>0.012162</v>
+        <v>-0.004384152000000005</v>
       </c>
       <c r="P32">
-        <v>0.02837799999999999</v>
+        <v>-0.01022968800000001</v>
       </c>
       <c r="Q32">
-        <v>0.133378</v>
+        <v>0.094770312</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1555643921104222</v>
+        <v>0.1580144194288711</v>
       </c>
       <c r="T32">
-        <v>0.7653259185575255</v>
+        <v>0.7824085932932142</v>
       </c>
       <c r="U32">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.3</v>
+        <v>0.2676717951501115</v>
       </c>
       <c r="W32">
-        <v>0.063</v>
+        <v>0.1075057804719636</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.503852846134725</v>
+        <v>0.8922393171670383</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1423567413522298</v>
+        <v>0.1433667413522298</v>
       </c>
       <c r="C33">
-        <v>1.682064249895672</v>
+        <v>1.625288634476754</v>
       </c>
       <c r="D33">
-        <v>2.605864249895672</v>
+        <v>2.578888634476754</v>
       </c>
       <c r="E33">
-        <v>0.9238</v>
+        <v>0.9536</v>
       </c>
       <c r="F33">
-        <v>0.9238</v>
+        <v>0.9536</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4115,37 +4115,37 @@
         <v>0.121</v>
       </c>
       <c r="M33">
-        <v>0.13561384</v>
+        <v>0.13998848</v>
       </c>
       <c r="N33">
-        <v>-0.01461384000000002</v>
+        <v>-0.01898848000000003</v>
       </c>
       <c r="O33">
-        <v>-0.004384152000000005</v>
+        <v>-0.005696544000000009</v>
       </c>
       <c r="P33">
-        <v>-0.01022968800000001</v>
+        <v>-0.01329193600000002</v>
       </c>
       <c r="Q33">
-        <v>0.094770312</v>
+        <v>0.09170806399999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1580144194288711</v>
+        <v>0.1596646314792957</v>
       </c>
       <c r="T33">
-        <v>0.7824085932932142</v>
+        <v>0.7939146020181146</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.2676717951501115</v>
+        <v>0.2593070515516705</v>
       </c>
       <c r="W33">
-        <v>0.1075057804719636</v>
+        <v>0.1087337248322148</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8922393171670383</v>
+        <v>0.8643568385055682</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1433667413522298</v>
+        <v>0.1443767413522298</v>
       </c>
       <c r="C34">
-        <v>1.625288634476754</v>
+        <v>1.569065793905116</v>
       </c>
       <c r="D34">
-        <v>2.578888634476754</v>
+        <v>2.552465793905117</v>
       </c>
       <c r="E34">
-        <v>0.9536</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="F34">
-        <v>0.9536</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4197,37 +4197,37 @@
         <v>0.121</v>
       </c>
       <c r="M34">
-        <v>0.13998848</v>
+        <v>0.14436312</v>
       </c>
       <c r="N34">
-        <v>-0.01898848000000003</v>
+        <v>-0.02336312000000001</v>
       </c>
       <c r="O34">
-        <v>-0.005696544000000009</v>
+        <v>-0.007008936000000005</v>
       </c>
       <c r="P34">
-        <v>-0.01329193600000002</v>
+        <v>-0.01635418400000001</v>
       </c>
       <c r="Q34">
-        <v>0.09170806399999999</v>
+        <v>0.088645816</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1596646314792957</v>
+        <v>0.161364103590927</v>
       </c>
       <c r="T34">
-        <v>0.7939146020181146</v>
+        <v>0.8057640736900267</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.2593070515516705</v>
+        <v>0.2514492621107108</v>
       </c>
       <c r="W34">
-        <v>0.1087337248322148</v>
+        <v>0.1098872483221477</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8643568385055682</v>
+        <v>0.8381642070357027</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1443767413522298</v>
+        <v>0.1453867413522298</v>
       </c>
       <c r="C35">
-        <v>1.569065793905116</v>
+        <v>1.513378909598641</v>
       </c>
       <c r="D35">
-        <v>2.552465793905117</v>
+        <v>2.526578909598641</v>
       </c>
       <c r="E35">
-        <v>0.9834000000000001</v>
+        <v>1.0132</v>
       </c>
       <c r="F35">
-        <v>0.9834000000000001</v>
+        <v>1.0132</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4279,37 +4279,37 @@
         <v>0.121</v>
       </c>
       <c r="M35">
-        <v>0.14436312</v>
+        <v>0.14873776</v>
       </c>
       <c r="N35">
-        <v>-0.02336312000000001</v>
+        <v>-0.02773776000000003</v>
       </c>
       <c r="O35">
-        <v>-0.007008936000000005</v>
+        <v>-0.008321328000000008</v>
       </c>
       <c r="P35">
-        <v>-0.01635418400000001</v>
+        <v>-0.01941643200000002</v>
       </c>
       <c r="Q35">
-        <v>0.088645816</v>
+        <v>0.085583568</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.161364103590927</v>
+        <v>0.1631150748574562</v>
       </c>
       <c r="T35">
-        <v>0.8057640736900267</v>
+        <v>0.8179726202610877</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.2514492621107108</v>
+        <v>0.2440536955780428</v>
       </c>
       <c r="W35">
-        <v>0.1098872483221477</v>
+        <v>0.1109729174891433</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8381642070357027</v>
+        <v>0.8135123185934761</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1453867413522298</v>
+        <v>0.1671808783644392</v>
       </c>
       <c r="C36">
-        <v>1.513378909598641</v>
+        <v>1.029927497037404</v>
       </c>
       <c r="D36">
-        <v>2.526578909598641</v>
+        <v>2.072927497037405</v>
       </c>
       <c r="E36">
-        <v>1.0132</v>
+        <v>1.043</v>
       </c>
       <c r="F36">
-        <v>1.0132</v>
+        <v>1.043</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4361,45 +4361,45 @@
         <v>0.121</v>
       </c>
       <c r="M36">
-        <v>0.14873776</v>
+        <v>0.2094344</v>
       </c>
       <c r="N36">
-        <v>-0.02773776000000003</v>
+        <v>-0.08843440000000005</v>
       </c>
       <c r="O36">
-        <v>-0.008321328000000008</v>
+        <v>-0.02653032000000001</v>
       </c>
       <c r="P36">
-        <v>-0.01941643200000002</v>
+        <v>-0.06190408000000004</v>
       </c>
       <c r="Q36">
-        <v>0.085583568</v>
+        <v>0.04309591999999997</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1631150748574562</v>
+        <v>0.1678185944894315</v>
       </c>
       <c r="T36">
-        <v>0.8179726202610877</v>
+        <v>0.8507676407006266</v>
       </c>
       <c r="U36">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.2440536955780428</v>
+        <v>0.1733239620616288</v>
       </c>
       <c r="W36">
-        <v>0.1109729174891433</v>
+        <v>0.1659965484180249</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.8135123185934761</v>
+        <v>0.5777465402054294</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1671808783644392</v>
+        <v>0.1687308783644392</v>
       </c>
       <c r="C37">
-        <v>1.029927497037404</v>
+        <v>0.9739905519251881</v>
       </c>
       <c r="D37">
-        <v>2.072927497037405</v>
+        <v>2.046790551925188</v>
       </c>
       <c r="E37">
-        <v>1.043</v>
+        <v>1.0728</v>
       </c>
       <c r="F37">
-        <v>1.043</v>
+        <v>1.0728</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4443,37 +4443,37 @@
         <v>0.121</v>
       </c>
       <c r="M37">
-        <v>0.2094344</v>
+        <v>0.21541824</v>
       </c>
       <c r="N37">
-        <v>-0.08843440000000005</v>
+        <v>-0.09441824000000004</v>
       </c>
       <c r="O37">
-        <v>-0.02653032000000001</v>
+        <v>-0.02832547200000001</v>
       </c>
       <c r="P37">
-        <v>-0.06190408000000004</v>
+        <v>-0.06609276800000002</v>
       </c>
       <c r="Q37">
-        <v>0.04309591999999997</v>
+        <v>0.03890723199999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1678185944894315</v>
+        <v>0.1697251350283289</v>
       </c>
       <c r="T37">
-        <v>0.8507676407006266</v>
+        <v>0.8640608850865739</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1733239620616288</v>
+        <v>0.1685094075599169</v>
       </c>
       <c r="W37">
-        <v>0.1659965484180249</v>
+        <v>0.1669633109619687</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5777465402054294</v>
+        <v>0.561698025199723</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1687308783644392</v>
+        <v>0.1702808783644392</v>
       </c>
       <c r="C38">
-        <v>0.9739905519251879</v>
+        <v>0.9187045062194696</v>
       </c>
       <c r="D38">
-        <v>2.046790551925188</v>
+        <v>2.02130450621947</v>
       </c>
       <c r="E38">
-        <v>1.0728</v>
+        <v>1.1026</v>
       </c>
       <c r="F38">
-        <v>1.0728</v>
+        <v>1.1026</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4525,37 +4525,37 @@
         <v>0.121</v>
       </c>
       <c r="M38">
-        <v>0.21541824</v>
+        <v>0.22140208</v>
       </c>
       <c r="N38">
-        <v>-0.09441824000000001</v>
+        <v>-0.10040208</v>
       </c>
       <c r="O38">
-        <v>-0.028325472</v>
+        <v>-0.030120624</v>
       </c>
       <c r="P38">
-        <v>-0.06609276800000001</v>
+        <v>-0.07028145600000001</v>
       </c>
       <c r="Q38">
-        <v>0.038907232</v>
+        <v>0.034718544</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1697251350283289</v>
+        <v>0.1716922006636992</v>
       </c>
       <c r="T38">
-        <v>0.8640608850865739</v>
+        <v>0.8777761372308052</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1685094075599169</v>
+        <v>0.1639550992474867</v>
       </c>
       <c r="W38">
-        <v>0.1669633109619687</v>
+        <v>0.1678778160711047</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.561698025199723</v>
+        <v>0.5465169974916224</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1702808783644392</v>
+        <v>0.1718308783644392</v>
       </c>
       <c r="C39">
-        <v>0.9187045062194696</v>
+        <v>0.864045344517997</v>
       </c>
       <c r="D39">
-        <v>2.02130450621947</v>
+        <v>1.996445344517997</v>
       </c>
       <c r="E39">
-        <v>1.1026</v>
+        <v>1.1324</v>
       </c>
       <c r="F39">
-        <v>1.1026</v>
+        <v>1.1324</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4607,37 +4607,37 @@
         <v>0.121</v>
       </c>
       <c r="M39">
-        <v>0.22140208</v>
+        <v>0.22738592</v>
       </c>
       <c r="N39">
-        <v>-0.10040208</v>
+        <v>-0.10638592</v>
       </c>
       <c r="O39">
-        <v>-0.030120624</v>
+        <v>-0.03191577600000001</v>
       </c>
       <c r="P39">
-        <v>-0.07028145600000001</v>
+        <v>-0.07447014400000002</v>
       </c>
       <c r="Q39">
-        <v>0.034718544</v>
+        <v>0.03052985599999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1716922006636992</v>
+        <v>0.1737227200292427</v>
       </c>
       <c r="T39">
-        <v>0.8777761372308052</v>
+        <v>0.8919338168635601</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1639550992474867</v>
+        <v>0.1596404913725528</v>
       </c>
       <c r="W39">
-        <v>0.1678778160711047</v>
+        <v>0.1687441893323914</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5465169974916224</v>
+        <v>0.5321349712418428</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1718308783644392</v>
+        <v>0.1733808783644392</v>
       </c>
       <c r="C40">
-        <v>0.864045344517997</v>
+        <v>0.8099902184859955</v>
       </c>
       <c r="D40">
-        <v>1.996445344517997</v>
+        <v>1.972190218485996</v>
       </c>
       <c r="E40">
-        <v>1.1324</v>
+        <v>1.1622</v>
       </c>
       <c r="F40">
-        <v>1.1324</v>
+        <v>1.1622</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4689,37 +4689,37 @@
         <v>0.121</v>
       </c>
       <c r="M40">
-        <v>0.22738592</v>
+        <v>0.23336976</v>
       </c>
       <c r="N40">
-        <v>-0.10638592</v>
+        <v>-0.11236976</v>
       </c>
       <c r="O40">
-        <v>-0.03191577600000001</v>
+        <v>-0.03371092800000001</v>
       </c>
       <c r="P40">
-        <v>-0.07447014400000002</v>
+        <v>-0.07865883200000004</v>
       </c>
       <c r="Q40">
-        <v>0.03052985599999999</v>
+        <v>0.02634116799999997</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1737227200292427</v>
+        <v>0.1758198138002139</v>
       </c>
       <c r="T40">
-        <v>0.8919338168635601</v>
+        <v>0.9065556827137823</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1596404913725528</v>
+        <v>0.1555471454399233</v>
       </c>
       <c r="W40">
-        <v>0.1687441893323914</v>
+        <v>0.1695661331956634</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5321349712418428</v>
+        <v>0.5184904847997442</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1733808783644392</v>
+        <v>0.1749308783644392</v>
       </c>
       <c r="C41">
-        <v>0.8099902184859955</v>
+        <v>0.7565173768127134</v>
       </c>
       <c r="D41">
-        <v>1.972190218485996</v>
+        <v>1.948517376812713</v>
       </c>
       <c r="E41">
-        <v>1.1622</v>
+        <v>1.192</v>
       </c>
       <c r="F41">
-        <v>1.1622</v>
+        <v>1.192</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4771,37 +4771,37 @@
         <v>0.121</v>
       </c>
       <c r="M41">
-        <v>0.23336976</v>
+        <v>0.2393536</v>
       </c>
       <c r="N41">
-        <v>-0.11236976</v>
+        <v>-0.1183536</v>
       </c>
       <c r="O41">
-        <v>-0.03371092800000001</v>
+        <v>-0.03550608</v>
       </c>
       <c r="P41">
-        <v>-0.07865883200000004</v>
+        <v>-0.08284752000000001</v>
       </c>
       <c r="Q41">
-        <v>0.02634116799999997</v>
+        <v>0.02215248</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1758198138002139</v>
+        <v>0.1779868106968841</v>
       </c>
       <c r="T41">
-        <v>0.9065556827137823</v>
+        <v>0.9216649440923455</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1555471454399233</v>
+        <v>0.1516584668039252</v>
       </c>
       <c r="W41">
-        <v>0.1695661331956634</v>
+        <v>0.1703469798657718</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5184904847997442</v>
+        <v>0.5055282226797508</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1749308783644392</v>
+        <v>0.191591150406717</v>
       </c>
       <c r="C42">
-        <v>0.7565173768127134</v>
+        <v>0.5040507095544944</v>
       </c>
       <c r="D42">
-        <v>1.948517376812713</v>
+        <v>1.725850709554494</v>
       </c>
       <c r="E42">
-        <v>1.192</v>
+        <v>1.2218</v>
       </c>
       <c r="F42">
-        <v>1.192</v>
+        <v>1.2218</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4853,45 +4853,45 @@
         <v>0.121</v>
       </c>
       <c r="M42">
-        <v>0.2393536</v>
+        <v>0.28810044</v>
       </c>
       <c r="N42">
-        <v>-0.1183536</v>
+        <v>-0.16710044</v>
       </c>
       <c r="O42">
-        <v>-0.03550608</v>
+        <v>-0.050130132</v>
       </c>
       <c r="P42">
-        <v>-0.08284752000000001</v>
+        <v>-0.116970308</v>
       </c>
       <c r="Q42">
-        <v>0.02215248</v>
+        <v>-0.01197030800000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1779868106968841</v>
+        <v>0.1815158617973022</v>
       </c>
       <c r="T42">
-        <v>0.9216649440923455</v>
+        <v>0.946271050163127</v>
       </c>
       <c r="U42">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.1516584668039252</v>
+        <v>0.1259977249600868</v>
       </c>
       <c r="W42">
-        <v>0.1703469798657718</v>
+        <v>0.2060897364544116</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.5055282226797508</v>
+        <v>0.4199924165336227</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.191591150406717</v>
+        <v>0.193491150406717</v>
       </c>
       <c r="C43">
-        <v>0.5040507095544944</v>
+        <v>0.4520481853062688</v>
       </c>
       <c r="D43">
-        <v>1.725850709554494</v>
+        <v>1.703648185306269</v>
       </c>
       <c r="E43">
-        <v>1.2218</v>
+        <v>1.2516</v>
       </c>
       <c r="F43">
-        <v>1.2218</v>
+        <v>1.2516</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4935,37 +4935,37 @@
         <v>0.121</v>
       </c>
       <c r="M43">
-        <v>0.28810044</v>
+        <v>0.29512728</v>
       </c>
       <c r="N43">
-        <v>-0.16710044</v>
+        <v>-0.1741272800000001</v>
       </c>
       <c r="O43">
-        <v>-0.050130132</v>
+        <v>-0.05223818400000001</v>
       </c>
       <c r="P43">
-        <v>-0.116970308</v>
+        <v>-0.121889096</v>
       </c>
       <c r="Q43">
-        <v>-0.01197030800000001</v>
+        <v>-0.01688909600000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1815158617973022</v>
+        <v>0.1838557904489798</v>
       </c>
       <c r="T43">
-        <v>0.946271050163127</v>
+        <v>0.9625860682693878</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.1259977249600868</v>
+        <v>0.1229977791277038</v>
       </c>
       <c r="W43">
-        <v>0.2060897364544116</v>
+        <v>0.2067971236816875</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4199924165336227</v>
+        <v>0.4099925970923459</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.193491150406717</v>
+        <v>0.195391150406717</v>
       </c>
       <c r="C44">
-        <v>0.4520481853062688</v>
+        <v>0.4006096622834752</v>
       </c>
       <c r="D44">
-        <v>1.703648185306269</v>
+        <v>1.682009662283475</v>
       </c>
       <c r="E44">
-        <v>1.2516</v>
+        <v>1.2814</v>
       </c>
       <c r="F44">
-        <v>1.2516</v>
+        <v>1.2814</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -5017,37 +5017,37 @@
         <v>0.121</v>
       </c>
       <c r="M44">
-        <v>0.29512728</v>
+        <v>0.30215412</v>
       </c>
       <c r="N44">
-        <v>-0.1741272800000001</v>
+        <v>-0.18115412</v>
       </c>
       <c r="O44">
-        <v>-0.05223818400000001</v>
+        <v>-0.05434623599999999</v>
       </c>
       <c r="P44">
-        <v>-0.121889096</v>
+        <v>-0.126807884</v>
       </c>
       <c r="Q44">
-        <v>-0.01688909600000002</v>
+        <v>-0.02180788399999997</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1838557904489798</v>
+        <v>0.1862778218603654</v>
       </c>
       <c r="T44">
-        <v>0.9625860682693875</v>
+        <v>0.9794735431513069</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.1229977791277038</v>
+        <v>0.1201373656596177</v>
       </c>
       <c r="W44">
-        <v>0.2067971236816875</v>
+        <v>0.2074716091774622</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4099925970923459</v>
+        <v>0.400457885532059</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.195391150406717</v>
+        <v>0.197291150406717</v>
       </c>
       <c r="C45">
-        <v>0.4006096622834752</v>
+        <v>0.349713919398438</v>
       </c>
       <c r="D45">
-        <v>1.682009662283475</v>
+        <v>1.660913919398438</v>
       </c>
       <c r="E45">
-        <v>1.2814</v>
+        <v>1.3112</v>
       </c>
       <c r="F45">
-        <v>1.2814</v>
+        <v>1.3112</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -5099,37 +5099,37 @@
         <v>0.121</v>
       </c>
       <c r="M45">
-        <v>0.30215412</v>
+        <v>0.30918096</v>
       </c>
       <c r="N45">
-        <v>-0.18115412</v>
+        <v>-0.18818096</v>
       </c>
       <c r="O45">
-        <v>-0.05434623599999999</v>
+        <v>-0.056454288</v>
       </c>
       <c r="P45">
-        <v>-0.126807884</v>
+        <v>-0.131726672</v>
       </c>
       <c r="Q45">
-        <v>-0.02180788399999997</v>
+        <v>-0.02672667200000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1862778218603654</v>
+        <v>0.1887863543935862</v>
       </c>
       <c r="T45">
-        <v>0.9794735431513069</v>
+        <v>0.9969641421361515</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.1201373656596177</v>
+        <v>0.1174069709855355</v>
       </c>
       <c r="W45">
-        <v>0.2074716091774622</v>
+        <v>0.2081154362416107</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.400457885532059</v>
+        <v>0.3913565699517848</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.197291150406717</v>
+        <v>0.199191150406717</v>
       </c>
       <c r="C46">
-        <v>0.349713919398438</v>
+        <v>0.2993407869948439</v>
       </c>
       <c r="D46">
-        <v>1.660913919398438</v>
+        <v>1.640340786994844</v>
       </c>
       <c r="E46">
-        <v>1.3112</v>
+        <v>1.341</v>
       </c>
       <c r="F46">
-        <v>1.3112</v>
+        <v>1.341</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5181,37 +5181,37 @@
         <v>0.121</v>
       </c>
       <c r="M46">
-        <v>0.30918096</v>
+        <v>0.3162078</v>
       </c>
       <c r="N46">
-        <v>-0.18818096</v>
+        <v>-0.1952078</v>
       </c>
       <c r="O46">
-        <v>-0.056454288</v>
+        <v>-0.05856233999999999</v>
       </c>
       <c r="P46">
-        <v>-0.131726672</v>
+        <v>-0.13664546</v>
       </c>
       <c r="Q46">
-        <v>-0.02672667200000001</v>
+        <v>-0.03164545999999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1887863543935862</v>
+        <v>0.1913861062916515</v>
       </c>
       <c r="T46">
-        <v>0.9969641421361515</v>
+        <v>1.015090762902263</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.1174069709855355</v>
+        <v>0.1147979271858569</v>
       </c>
       <c r="W46">
-        <v>0.2081154362416107</v>
+        <v>0.208730648769575</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3913565699517848</v>
+        <v>0.3826597572861896</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.199191150406717</v>
+        <v>0.201091150406717</v>
       </c>
       <c r="C47">
-        <v>0.2993407869948439</v>
+        <v>0.2494710825259958</v>
       </c>
       <c r="D47">
-        <v>1.640340786994844</v>
+        <v>1.620271082525996</v>
       </c>
       <c r="E47">
-        <v>1.341</v>
+        <v>1.3708</v>
       </c>
       <c r="F47">
-        <v>1.341</v>
+        <v>1.3708</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5263,37 +5263,37 @@
         <v>0.121</v>
       </c>
       <c r="M47">
-        <v>0.3162078</v>
+        <v>0.32323464</v>
       </c>
       <c r="N47">
-        <v>-0.1952078</v>
+        <v>-0.20223464</v>
       </c>
       <c r="O47">
-        <v>-0.05856233999999999</v>
+        <v>-0.060670392</v>
       </c>
       <c r="P47">
-        <v>-0.13664546</v>
+        <v>-0.141564248</v>
       </c>
       <c r="Q47">
-        <v>-0.03164545999999999</v>
+        <v>-0.03656424799999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1913861062916515</v>
+        <v>0.1940821452970524</v>
       </c>
       <c r="T47">
-        <v>1.015090762902263</v>
+        <v>1.033888739993046</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.1147979271858569</v>
+        <v>0.1123023200731209</v>
       </c>
       <c r="W47">
-        <v>0.208730648769575</v>
+        <v>0.2093191129267581</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3826597572861896</v>
+        <v>0.3743410669104029</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.201091150406717</v>
+        <v>0.2029911504067171</v>
       </c>
       <c r="C48">
-        <v>0.2494710825259958</v>
+        <v>0.2000865508978853</v>
       </c>
       <c r="D48">
-        <v>1.620271082525996</v>
+        <v>1.600686550897885</v>
       </c>
       <c r="E48">
-        <v>1.3708</v>
+        <v>1.4006</v>
       </c>
       <c r="F48">
-        <v>1.3708</v>
+        <v>1.4006</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5345,37 +5345,37 @@
         <v>0.121</v>
       </c>
       <c r="M48">
-        <v>0.32323464</v>
+        <v>0.3302614800000001</v>
       </c>
       <c r="N48">
-        <v>-0.20223464</v>
+        <v>-0.2092614800000001</v>
       </c>
       <c r="O48">
-        <v>-0.060670392</v>
+        <v>-0.06277844400000002</v>
       </c>
       <c r="P48">
-        <v>-0.141564248</v>
+        <v>-0.146483036</v>
       </c>
       <c r="Q48">
-        <v>-0.03656424799999999</v>
+        <v>-0.04148303600000003</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1940821452970524</v>
+        <v>0.1968799216234119</v>
       </c>
       <c r="T48">
-        <v>1.033888739993046</v>
+        <v>1.053396074709896</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.1123023200731209</v>
+        <v>0.1099129090077353</v>
       </c>
       <c r="W48">
-        <v>0.2093191129267581</v>
+        <v>0.209882536055976</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3743410669104029</v>
+        <v>0.3663763633591177</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2029911504067171</v>
+        <v>0.204891150406717</v>
       </c>
       <c r="C49">
-        <v>0.2000865508978853</v>
+        <v>0.1511698090871005</v>
       </c>
       <c r="D49">
-        <v>1.600686550897885</v>
+        <v>1.581569809087101</v>
       </c>
       <c r="E49">
-        <v>1.4006</v>
+        <v>1.4304</v>
       </c>
       <c r="F49">
-        <v>1.4006</v>
+        <v>1.4304</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5427,37 +5427,37 @@
         <v>0.121</v>
       </c>
       <c r="M49">
-        <v>0.3302614800000001</v>
+        <v>0.33728832</v>
       </c>
       <c r="N49">
-        <v>-0.2092614800000001</v>
+        <v>-0.21628832</v>
       </c>
       <c r="O49">
-        <v>-0.06277844400000002</v>
+        <v>-0.064886496</v>
       </c>
       <c r="P49">
-        <v>-0.146483036</v>
+        <v>-0.151401824</v>
       </c>
       <c r="Q49">
-        <v>-0.04148303600000003</v>
+        <v>-0.04640182400000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1968799216234119</v>
+        <v>0.1997853047315544</v>
       </c>
       <c r="T49">
-        <v>1.053396074709896</v>
+        <v>1.07365369153124</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.1099129090077353</v>
+        <v>0.1076230567367408</v>
       </c>
       <c r="W49">
-        <v>0.209882536055976</v>
+        <v>0.2104224832214765</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3663763633591177</v>
+        <v>0.3587435224558028</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.204891150406717</v>
+        <v>0.206791150406717</v>
       </c>
       <c r="C50">
-        <v>0.1511698090871008</v>
+        <v>0.1027042946804149</v>
       </c>
       <c r="D50">
-        <v>1.581569809087101</v>
+        <v>1.562904294680415</v>
       </c>
       <c r="E50">
-        <v>1.4304</v>
+        <v>1.4602</v>
       </c>
       <c r="F50">
-        <v>1.4304</v>
+        <v>1.4602</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5509,37 +5509,37 @@
         <v>0.121</v>
       </c>
       <c r="M50">
-        <v>0.33728832</v>
+        <v>0.34431516</v>
       </c>
       <c r="N50">
-        <v>-0.21628832</v>
+        <v>-0.22331516</v>
       </c>
       <c r="O50">
-        <v>-0.06488649599999999</v>
+        <v>-0.066994548</v>
       </c>
       <c r="P50">
-        <v>-0.151401824</v>
+        <v>-0.156320612</v>
       </c>
       <c r="Q50">
-        <v>-0.04640182399999998</v>
+        <v>-0.05132061200000002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1997853047315544</v>
+        <v>0.2028046244321731</v>
       </c>
       <c r="T50">
-        <v>1.07365369153124</v>
+        <v>1.094705724698519</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.1076230567367408</v>
+        <v>0.1054266678237461</v>
       </c>
       <c r="W50">
-        <v>0.2104224832214765</v>
+        <v>0.2109403917271607</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3587435224558028</v>
+        <v>0.3514222260791537</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.206791150406717</v>
+        <v>0.208691150406717</v>
       </c>
       <c r="C51">
-        <v>0.1027042946804149</v>
+        <v>0.05467421801585526</v>
       </c>
       <c r="D51">
-        <v>1.562904294680415</v>
+        <v>1.544674218015855</v>
       </c>
       <c r="E51">
-        <v>1.4602</v>
+        <v>1.49</v>
       </c>
       <c r="F51">
-        <v>1.4602</v>
+        <v>1.49</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5591,37 +5591,37 @@
         <v>0.121</v>
       </c>
       <c r="M51">
-        <v>0.34431516</v>
+        <v>0.351342</v>
       </c>
       <c r="N51">
-        <v>-0.22331516</v>
+        <v>-0.230342</v>
       </c>
       <c r="O51">
-        <v>-0.066994548</v>
+        <v>-0.0691026</v>
       </c>
       <c r="P51">
-        <v>-0.156320612</v>
+        <v>-0.1612394</v>
       </c>
       <c r="Q51">
-        <v>-0.05132061200000002</v>
+        <v>-0.05623939999999997</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2028046244321731</v>
+        <v>0.2059447169208166</v>
       </c>
       <c r="T51">
-        <v>1.094705724698519</v>
+        <v>1.11659983919249</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.1054266678237461</v>
+        <v>0.1033181344672712</v>
       </c>
       <c r="W51">
-        <v>0.2109403917271607</v>
+        <v>0.2114375838926175</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3514222260791537</v>
+        <v>0.3443937815575707</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.208691150406717</v>
+        <v>0.210591150406717</v>
       </c>
       <c r="C52">
-        <v>0.05467421801585526</v>
+        <v>0.007064517634574718</v>
       </c>
       <c r="D52">
-        <v>1.544674218015855</v>
+        <v>1.526864517634575</v>
       </c>
       <c r="E52">
-        <v>1.49</v>
+        <v>1.5198</v>
       </c>
       <c r="F52">
-        <v>1.49</v>
+        <v>1.5198</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5673,37 +5673,37 @@
         <v>0.121</v>
       </c>
       <c r="M52">
-        <v>0.351342</v>
+        <v>0.35836884</v>
       </c>
       <c r="N52">
-        <v>-0.230342</v>
+        <v>-0.23736884</v>
       </c>
       <c r="O52">
-        <v>-0.0691026</v>
+        <v>-0.071210652</v>
       </c>
       <c r="P52">
-        <v>-0.1612394</v>
+        <v>-0.166158188</v>
       </c>
       <c r="Q52">
-        <v>-0.05623939999999997</v>
+        <v>-0.06115818800000003</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2059447169208166</v>
+        <v>0.2092129764498128</v>
       </c>
       <c r="T52">
-        <v>1.11659983919249</v>
+        <v>1.139387591012745</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.1033181344672712</v>
+        <v>0.1012922886934031</v>
       </c>
       <c r="W52">
-        <v>0.2114375838926175</v>
+        <v>0.2119152783260956</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3443937815575707</v>
+        <v>0.3376409623113438</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.210591150406717</v>
+        <v>0.212491150406717</v>
       </c>
       <c r="C53">
-        <v>0.007064517634574718</v>
+        <v>-0.0401391812206271</v>
       </c>
       <c r="D53">
-        <v>1.526864517634575</v>
+        <v>1.509460818779373</v>
       </c>
       <c r="E53">
-        <v>1.5198</v>
+        <v>1.5496</v>
       </c>
       <c r="F53">
-        <v>1.5198</v>
+        <v>1.5496</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5755,37 +5755,37 @@
         <v>0.121</v>
       </c>
       <c r="M53">
-        <v>0.35836884</v>
+        <v>0.3653956800000001</v>
       </c>
       <c r="N53">
-        <v>-0.23736884</v>
+        <v>-0.2443956800000001</v>
       </c>
       <c r="O53">
-        <v>-0.071210652</v>
+        <v>-0.07331870400000001</v>
       </c>
       <c r="P53">
-        <v>-0.166158188</v>
+        <v>-0.171076976</v>
       </c>
       <c r="Q53">
-        <v>-0.06115818800000003</v>
+        <v>-0.06607697600000004</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2092129764498128</v>
+        <v>0.2126174134591839</v>
       </c>
       <c r="T53">
-        <v>1.139387591012745</v>
+        <v>1.163124832492177</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1012922886934031</v>
+        <v>0.09934436006468382</v>
       </c>
       <c r="W53">
-        <v>0.2119152783260956</v>
+        <v>0.2123745998967476</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3376409623113438</v>
+        <v>0.3311478668822795</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.212491150406717</v>
+        <v>0.214391150406717</v>
       </c>
       <c r="C54">
-        <v>-0.0401391812206271</v>
+        <v>-0.08695060530049137</v>
       </c>
       <c r="D54">
-        <v>1.509460818779373</v>
+        <v>1.492449394699509</v>
       </c>
       <c r="E54">
-        <v>1.5496</v>
+        <v>1.5794</v>
       </c>
       <c r="F54">
-        <v>1.5496</v>
+        <v>1.5794</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5837,37 +5837,37 @@
         <v>0.121</v>
       </c>
       <c r="M54">
-        <v>0.3653956800000001</v>
+        <v>0.37242252</v>
       </c>
       <c r="N54">
-        <v>-0.2443956800000001</v>
+        <v>-0.25142252</v>
       </c>
       <c r="O54">
-        <v>-0.07331870400000001</v>
+        <v>-0.07542675600000001</v>
       </c>
       <c r="P54">
-        <v>-0.171076976</v>
+        <v>-0.175995764</v>
       </c>
       <c r="Q54">
-        <v>-0.06607697600000004</v>
+        <v>-0.07099576400000002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2126174134591839</v>
+        <v>0.2161667201285283</v>
       </c>
       <c r="T54">
-        <v>1.163124832492177</v>
+        <v>1.187872169353712</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.09934436006468382</v>
+        <v>0.09746993817667093</v>
       </c>
       <c r="W54">
-        <v>0.2123745998967476</v>
+        <v>0.212816588577941</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3311478668822795</v>
+        <v>0.3248997939222364</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.214391150406717</v>
+        <v>0.216291150406717</v>
       </c>
       <c r="C55">
-        <v>-0.08695060530049137</v>
+        <v>-0.1333828694571029</v>
       </c>
       <c r="D55">
-        <v>1.492449394699509</v>
+        <v>1.475817130542897</v>
       </c>
       <c r="E55">
-        <v>1.5794</v>
+        <v>1.6092</v>
       </c>
       <c r="F55">
-        <v>1.5794</v>
+        <v>1.6092</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5919,37 +5919,37 @@
         <v>0.121</v>
       </c>
       <c r="M55">
-        <v>0.37242252</v>
+        <v>0.3794493600000001</v>
       </c>
       <c r="N55">
-        <v>-0.25142252</v>
+        <v>-0.2584493600000001</v>
       </c>
       <c r="O55">
-        <v>-0.07542675600000001</v>
+        <v>-0.07753480800000002</v>
       </c>
       <c r="P55">
-        <v>-0.175995764</v>
+        <v>-0.1809145520000001</v>
       </c>
       <c r="Q55">
-        <v>-0.07099576400000002</v>
+        <v>-0.07591455200000005</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2161667201285283</v>
+        <v>0.2198703444791485</v>
       </c>
       <c r="T55">
-        <v>1.187872169353712</v>
+        <v>1.213695477383141</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.09746993817667093</v>
+        <v>0.09566493932154739</v>
       </c>
       <c r="W55">
-        <v>0.212816588577941</v>
+        <v>0.2132422073079791</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3248997939222364</v>
+        <v>0.3188831310718246</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.216291150406717</v>
+        <v>0.218191150406717</v>
       </c>
       <c r="C56">
-        <v>-0.1333828694571029</v>
+        <v>-0.1794485103639354</v>
       </c>
       <c r="D56">
-        <v>1.475817130542897</v>
+        <v>1.459551489636065</v>
       </c>
       <c r="E56">
-        <v>1.6092</v>
+        <v>1.639</v>
       </c>
       <c r="F56">
-        <v>1.6092</v>
+        <v>1.639</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -6001,37 +6001,37 @@
         <v>0.121</v>
       </c>
       <c r="M56">
-        <v>0.3794493600000001</v>
+        <v>0.3864762</v>
       </c>
       <c r="N56">
-        <v>-0.2584493600000001</v>
+        <v>-0.2654762</v>
       </c>
       <c r="O56">
-        <v>-0.07753480800000002</v>
+        <v>-0.07964286</v>
       </c>
       <c r="P56">
-        <v>-0.1809145520000001</v>
+        <v>-0.18583334</v>
       </c>
       <c r="Q56">
-        <v>-0.07591455200000005</v>
+        <v>-0.08083334</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2198703444791485</v>
+        <v>0.2237385743564629</v>
       </c>
       <c r="T56">
-        <v>1.213695477383141</v>
+        <v>1.240666487991655</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.09566493932154739</v>
+        <v>0.09392557678842836</v>
       </c>
       <c r="W56">
-        <v>0.2132422073079791</v>
+        <v>0.2136523489932886</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3188831310718246</v>
+        <v>0.3130852559614279</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.218191150406717</v>
+        <v>0.220091150406717</v>
       </c>
       <c r="C57">
-        <v>-0.1794485103639354</v>
+        <v>-0.225159518030345</v>
       </c>
       <c r="D57">
-        <v>1.459551489636065</v>
+        <v>1.443640481969655</v>
       </c>
       <c r="E57">
-        <v>1.639</v>
+        <v>1.6688</v>
       </c>
       <c r="F57">
-        <v>1.639</v>
+        <v>1.6688</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -6083,37 +6083,37 @@
         <v>0.121</v>
       </c>
       <c r="M57">
-        <v>0.3864762</v>
+        <v>0.39350304</v>
       </c>
       <c r="N57">
-        <v>-0.2654762</v>
+        <v>-0.27250304</v>
       </c>
       <c r="O57">
-        <v>-0.07964286</v>
+        <v>-0.08175091200000001</v>
       </c>
       <c r="P57">
-        <v>-0.18583334</v>
+        <v>-0.190752128</v>
       </c>
       <c r="Q57">
-        <v>-0.08083334</v>
+        <v>-0.08575212800000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2237385743564629</v>
+        <v>0.2277826328645643</v>
       </c>
       <c r="T57">
-        <v>1.240666487991655</v>
+        <v>1.268863453627829</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.09392557678842836</v>
+        <v>0.09224833434577785</v>
       </c>
       <c r="W57">
-        <v>0.2136523489932886</v>
+        <v>0.2140478427612656</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3130852559614279</v>
+        <v>0.3074944478192595</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.220091150406717</v>
+        <v>0.221991150406717</v>
       </c>
       <c r="C58">
-        <v>-0.225159518030345</v>
+        <v>-0.2705273652769893</v>
       </c>
       <c r="D58">
-        <v>1.443640481969655</v>
+        <v>1.428072634723011</v>
       </c>
       <c r="E58">
-        <v>1.6688</v>
+        <v>1.6986</v>
       </c>
       <c r="F58">
-        <v>1.6688</v>
+        <v>1.6986</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6165,37 +6165,37 @@
         <v>0.121</v>
       </c>
       <c r="M58">
-        <v>0.39350304</v>
+        <v>0.4005298800000001</v>
       </c>
       <c r="N58">
-        <v>-0.27250304</v>
+        <v>-0.2795298800000001</v>
       </c>
       <c r="O58">
-        <v>-0.08175091200000001</v>
+        <v>-0.08385896400000002</v>
       </c>
       <c r="P58">
-        <v>-0.190752128</v>
+        <v>-0.195670916</v>
       </c>
       <c r="Q58">
-        <v>-0.08575212800000001</v>
+        <v>-0.09067091600000002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2277826328645643</v>
+        <v>0.2320147871172286</v>
       </c>
       <c r="T58">
-        <v>1.268863453627829</v>
+        <v>1.298371906037779</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.09224833434577785</v>
+        <v>0.09062994251515016</v>
       </c>
       <c r="W58">
-        <v>0.2140478427612656</v>
+        <v>0.2144294595549276</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3074944478192595</v>
+        <v>0.3020998083838339</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.221991150406717</v>
+        <v>0.223891150406717</v>
       </c>
       <c r="C59">
-        <v>-0.2705273652769893</v>
+        <v>-0.3155630353244743</v>
       </c>
       <c r="D59">
-        <v>1.428072634723011</v>
+        <v>1.412836964675526</v>
       </c>
       <c r="E59">
-        <v>1.6986</v>
+        <v>1.7284</v>
       </c>
       <c r="F59">
-        <v>1.6986</v>
+        <v>1.7284</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6247,37 +6247,37 @@
         <v>0.121</v>
       </c>
       <c r="M59">
-        <v>0.4005298800000001</v>
+        <v>0.40755672</v>
       </c>
       <c r="N59">
-        <v>-0.2795298800000001</v>
+        <v>-0.28655672</v>
       </c>
       <c r="O59">
-        <v>-0.08385896400000002</v>
+        <v>-0.08596701600000001</v>
       </c>
       <c r="P59">
-        <v>-0.195670916</v>
+        <v>-0.200589704</v>
       </c>
       <c r="Q59">
-        <v>-0.09067091600000002</v>
+        <v>-0.09558970400000003</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2320147871172286</v>
+        <v>0.2364484725247817</v>
       </c>
       <c r="T59">
-        <v>1.298371906037779</v>
+        <v>1.329285522848202</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.09062994251515016</v>
+        <v>0.08906735729937172</v>
       </c>
       <c r="W59">
-        <v>0.2144294595549276</v>
+        <v>0.2147979171488081</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3020998083838339</v>
+        <v>0.2968911909979057</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.223891150406717</v>
+        <v>0.225791150406717</v>
       </c>
       <c r="C60">
-        <v>-0.3155630353244738</v>
+        <v>-0.360277047634622</v>
       </c>
       <c r="D60">
-        <v>1.412836964675526</v>
+        <v>1.397922952365378</v>
       </c>
       <c r="E60">
-        <v>1.7284</v>
+        <v>1.7582</v>
       </c>
       <c r="F60">
-        <v>1.7284</v>
+        <v>1.7582</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6329,37 +6329,37 @@
         <v>0.121</v>
       </c>
       <c r="M60">
-        <v>0.40755672</v>
+        <v>0.41458356</v>
       </c>
       <c r="N60">
-        <v>-0.28655672</v>
+        <v>-0.29358356</v>
       </c>
       <c r="O60">
-        <v>-0.08596701599999999</v>
+        <v>-0.08807506800000001</v>
       </c>
       <c r="P60">
-        <v>-0.200589704</v>
+        <v>-0.205508492</v>
       </c>
       <c r="Q60">
-        <v>-0.09558970399999997</v>
+        <v>-0.100508492</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2364484725247816</v>
+        <v>0.2410984352692885</v>
       </c>
       <c r="T60">
-        <v>1.329285522848202</v>
+        <v>1.361707120966451</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.08906735729937174</v>
+        <v>0.08755774107395864</v>
       </c>
       <c r="W60">
-        <v>0.2147979171488081</v>
+        <v>0.2151538846547606</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2968911909979057</v>
+        <v>0.2918591369131954</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.225791150406717</v>
+        <v>0.227691150406717</v>
       </c>
       <c r="C61">
-        <v>-0.360277047634622</v>
+        <v>-0.4046794821321507</v>
       </c>
       <c r="D61">
-        <v>1.397922952365378</v>
+        <v>1.383320517867849</v>
       </c>
       <c r="E61">
-        <v>1.7582</v>
+        <v>1.788</v>
       </c>
       <c r="F61">
-        <v>1.7582</v>
+        <v>1.788</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6411,37 +6411,37 @@
         <v>0.121</v>
       </c>
       <c r="M61">
-        <v>0.41458356</v>
+        <v>0.4216104000000001</v>
       </c>
       <c r="N61">
-        <v>-0.29358356</v>
+        <v>-0.3006104000000001</v>
       </c>
       <c r="O61">
-        <v>-0.08807506800000001</v>
+        <v>-0.09018312000000002</v>
       </c>
       <c r="P61">
-        <v>-0.205508492</v>
+        <v>-0.21042728</v>
       </c>
       <c r="Q61">
-        <v>-0.100508492</v>
+        <v>-0.10542728</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2410984352692885</v>
+        <v>0.2459808961510207</v>
       </c>
       <c r="T61">
-        <v>1.361707120966451</v>
+        <v>1.395749798990612</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08755774107395864</v>
+        <v>0.08609844538939267</v>
       </c>
       <c r="W61">
-        <v>0.2151538846547606</v>
+        <v>0.2154979865771812</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2918591369131954</v>
+        <v>0.2869948179646422</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.227691150406717</v>
+        <v>0.229591150406717</v>
       </c>
       <c r="C62">
-        <v>-0.4046794821321507</v>
+        <v>-0.4487800019239503</v>
       </c>
       <c r="D62">
-        <v>1.383320517867849</v>
+        <v>1.36901999807605</v>
       </c>
       <c r="E62">
-        <v>1.788</v>
+        <v>1.8178</v>
       </c>
       <c r="F62">
-        <v>1.788</v>
+        <v>1.8178</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6493,37 +6493,37 @@
         <v>0.121</v>
       </c>
       <c r="M62">
-        <v>0.4216104000000001</v>
+        <v>0.42863724</v>
       </c>
       <c r="N62">
-        <v>-0.3006104000000001</v>
+        <v>-0.30763724</v>
       </c>
       <c r="O62">
-        <v>-0.09018312000000002</v>
+        <v>-0.09229117199999999</v>
       </c>
       <c r="P62">
-        <v>-0.21042728</v>
+        <v>-0.215346068</v>
       </c>
       <c r="Q62">
-        <v>-0.10542728</v>
+        <v>-0.110346068</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2459808961510207</v>
+        <v>0.2511137396420726</v>
       </c>
       <c r="T62">
-        <v>1.395749798990612</v>
+        <v>1.431538255374987</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.08609844538939267</v>
+        <v>0.08468699546497641</v>
       </c>
       <c r="W62">
-        <v>0.2154979865771812</v>
+        <v>0.2158308064693586</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2869948179646422</v>
+        <v>0.2822899848832546</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.229591150406717</v>
+        <v>0.231491150406717</v>
       </c>
       <c r="C63">
-        <v>-0.4487800019239503</v>
+        <v>-0.492587874623577</v>
       </c>
       <c r="D63">
-        <v>1.36901999807605</v>
+        <v>1.355012125376423</v>
       </c>
       <c r="E63">
-        <v>1.8178</v>
+        <v>1.8476</v>
       </c>
       <c r="F63">
-        <v>1.8178</v>
+        <v>1.8476</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6575,37 +6575,37 @@
         <v>0.121</v>
       </c>
       <c r="M63">
-        <v>0.42863724</v>
+        <v>0.43566408</v>
       </c>
       <c r="N63">
-        <v>-0.30763724</v>
+        <v>-0.31466408</v>
       </c>
       <c r="O63">
-        <v>-0.09229117199999999</v>
+        <v>-0.094399224</v>
       </c>
       <c r="P63">
-        <v>-0.215346068</v>
+        <v>-0.220264856</v>
       </c>
       <c r="Q63">
-        <v>-0.110346068</v>
+        <v>-0.115264856</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2511137396420726</v>
+        <v>0.2565167327905481</v>
       </c>
       <c r="T63">
-        <v>1.431538255374987</v>
+        <v>1.46921031472696</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.08468699546497641</v>
+        <v>0.08332107618328322</v>
       </c>
       <c r="W63">
-        <v>0.2158308064693586</v>
+        <v>0.2161528902359818</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2822899848832546</v>
+        <v>0.2777369206109441</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.231491150406717</v>
+        <v>0.233391150406717</v>
       </c>
       <c r="C64">
-        <v>-0.492587874623577</v>
+        <v>-0.536111992379843</v>
       </c>
       <c r="D64">
-        <v>1.355012125376423</v>
+        <v>1.341288007620157</v>
       </c>
       <c r="E64">
-        <v>1.8476</v>
+        <v>1.8774</v>
       </c>
       <c r="F64">
-        <v>1.8476</v>
+        <v>1.8774</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6657,37 +6657,37 @@
         <v>0.121</v>
       </c>
       <c r="M64">
-        <v>0.43566408</v>
+        <v>0.44269092</v>
       </c>
       <c r="N64">
-        <v>-0.31466408</v>
+        <v>-0.32169092</v>
       </c>
       <c r="O64">
-        <v>-0.094399224</v>
+        <v>-0.09650727599999999</v>
       </c>
       <c r="P64">
-        <v>-0.220264856</v>
+        <v>-0.225183644</v>
       </c>
       <c r="Q64">
-        <v>-0.115264856</v>
+        <v>-0.120183644</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2565167327905481</v>
+        <v>0.2622117796227251</v>
       </c>
       <c r="T64">
-        <v>1.46921031472696</v>
+        <v>1.508918701611472</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08332107618328322</v>
+        <v>0.08199851941846921</v>
       </c>
       <c r="W64">
-        <v>0.2161528902359818</v>
+        <v>0.216464749121125</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2777369206109441</v>
+        <v>0.2733283980615641</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.233391150406717</v>
+        <v>0.235291150406717</v>
       </c>
       <c r="C65">
-        <v>-0.536111992379843</v>
+        <v>-0.5793608907004688</v>
       </c>
       <c r="D65">
-        <v>1.341288007620157</v>
+        <v>1.327839109299531</v>
       </c>
       <c r="E65">
-        <v>1.8774</v>
+        <v>1.9072</v>
       </c>
       <c r="F65">
-        <v>1.8774</v>
+        <v>1.9072</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6739,37 +6739,37 @@
         <v>0.121</v>
       </c>
       <c r="M65">
-        <v>0.44269092</v>
+        <v>0.44971776</v>
       </c>
       <c r="N65">
-        <v>-0.32169092</v>
+        <v>-0.32871776</v>
       </c>
       <c r="O65">
-        <v>-0.09650727599999999</v>
+        <v>-0.098615328</v>
       </c>
       <c r="P65">
-        <v>-0.225183644</v>
+        <v>-0.230102432</v>
       </c>
       <c r="Q65">
-        <v>-0.120183644</v>
+        <v>-0.125102432</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2622117796227251</v>
+        <v>0.2682232179455786</v>
       </c>
       <c r="T65">
-        <v>1.508918701611472</v>
+        <v>1.550833109989569</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08199851941846921</v>
+        <v>0.08071729255255562</v>
       </c>
       <c r="W65">
-        <v>0.216464749121125</v>
+        <v>0.2167668624161074</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2733283980615641</v>
+        <v>0.2690576418418521</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.235291150406717</v>
+        <v>0.237191150406717</v>
       </c>
       <c r="C66">
-        <v>-0.5793608907004688</v>
+        <v>-0.6223427661545209</v>
       </c>
       <c r="D66">
-        <v>1.327839109299531</v>
+        <v>1.314657233845479</v>
       </c>
       <c r="E66">
-        <v>1.9072</v>
+        <v>1.937</v>
       </c>
       <c r="F66">
-        <v>1.9072</v>
+        <v>1.937</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6821,37 +6821,37 @@
         <v>0.121</v>
       </c>
       <c r="M66">
-        <v>0.44971776</v>
+        <v>0.4567446000000001</v>
       </c>
       <c r="N66">
-        <v>-0.32871776</v>
+        <v>-0.3357446000000001</v>
       </c>
       <c r="O66">
-        <v>-0.098615328</v>
+        <v>-0.10072338</v>
       </c>
       <c r="P66">
-        <v>-0.230102432</v>
+        <v>-0.23502122</v>
       </c>
       <c r="Q66">
-        <v>-0.125102432</v>
+        <v>-0.13002122</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2682232179455786</v>
+        <v>0.274578167029738</v>
       </c>
       <c r="T66">
-        <v>1.550833109989569</v>
+        <v>1.595142627417843</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.08071729255255562</v>
+        <v>0.07947548805174708</v>
       </c>
       <c r="W66">
-        <v>0.2167668624161074</v>
+        <v>0.2170596799173981</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2690576418418521</v>
+        <v>0.2649182935058235</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.237191150406717</v>
+        <v>0.239091150406717</v>
       </c>
       <c r="C67">
-        <v>-0.6223427661545209</v>
+        <v>-0.6650654930307929</v>
       </c>
       <c r="D67">
-        <v>1.314657233845479</v>
+        <v>1.301734506969207</v>
       </c>
       <c r="E67">
-        <v>1.937</v>
+        <v>1.9668</v>
       </c>
       <c r="F67">
-        <v>1.937</v>
+        <v>1.9668</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6903,37 +6903,37 @@
         <v>0.121</v>
       </c>
       <c r="M67">
-        <v>0.4567446000000001</v>
+        <v>0.46377144</v>
       </c>
       <c r="N67">
-        <v>-0.3357446000000001</v>
+        <v>-0.34277144</v>
       </c>
       <c r="O67">
-        <v>-0.10072338</v>
+        <v>-0.102831432</v>
       </c>
       <c r="P67">
-        <v>-0.23502122</v>
+        <v>-0.239940008</v>
       </c>
       <c r="Q67">
-        <v>-0.13002122</v>
+        <v>-0.134940008</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.274578167029738</v>
+        <v>0.2813069366482597</v>
       </c>
       <c r="T67">
-        <v>1.595142627417843</v>
+        <v>1.642058587047779</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07947548805174708</v>
+        <v>0.07827131399035696</v>
       </c>
       <c r="W67">
-        <v>0.2170596799173981</v>
+        <v>0.2173436241610739</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2649182935058235</v>
+        <v>0.2609043799678565</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.239091150406717</v>
+        <v>0.240991150406717</v>
       </c>
       <c r="C68">
-        <v>-0.6650654930307929</v>
+        <v>-0.7075366390232622</v>
       </c>
       <c r="D68">
-        <v>1.301734506969207</v>
+        <v>1.289063360976738</v>
       </c>
       <c r="E68">
-        <v>1.9668</v>
+        <v>1.9966</v>
       </c>
       <c r="F68">
-        <v>1.9668</v>
+        <v>1.9966</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6985,37 +6985,37 @@
         <v>0.121</v>
       </c>
       <c r="M68">
-        <v>0.46377144</v>
+        <v>0.4707982800000001</v>
       </c>
       <c r="N68">
-        <v>-0.34277144</v>
+        <v>-0.3497982800000001</v>
       </c>
       <c r="O68">
-        <v>-0.102831432</v>
+        <v>-0.104939484</v>
       </c>
       <c r="P68">
-        <v>-0.239940008</v>
+        <v>-0.244858796</v>
       </c>
       <c r="Q68">
-        <v>-0.134940008</v>
+        <v>-0.139858796</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2813069366482597</v>
+        <v>0.2884435104860857</v>
       </c>
       <c r="T68">
-        <v>1.642058587047779</v>
+        <v>1.691817938170439</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07827131399035696</v>
+        <v>0.0771030854233367</v>
       </c>
       <c r="W68">
-        <v>0.2173436241610739</v>
+        <v>0.2176190924571772</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2609043799678565</v>
+        <v>0.2570102847444556</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.240991150406717</v>
+        <v>0.242891150406717</v>
       </c>
       <c r="C69">
-        <v>-0.7075366390232622</v>
+        <v>-0.7497634800092812</v>
       </c>
       <c r="D69">
-        <v>1.289063360976738</v>
+        <v>1.276636519990719</v>
       </c>
       <c r="E69">
-        <v>1.9966</v>
+        <v>2.0264</v>
       </c>
       <c r="F69">
-        <v>1.9966</v>
+        <v>2.0264</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -7067,37 +7067,37 @@
         <v>0.121</v>
       </c>
       <c r="M69">
-        <v>0.4707982800000001</v>
+        <v>0.47782512</v>
       </c>
       <c r="N69">
-        <v>-0.3497982800000001</v>
+        <v>-0.3568251200000001</v>
       </c>
       <c r="O69">
-        <v>-0.104939484</v>
+        <v>-0.107047536</v>
       </c>
       <c r="P69">
-        <v>-0.244858796</v>
+        <v>-0.2497775840000001</v>
       </c>
       <c r="Q69">
-        <v>-0.139858796</v>
+        <v>-0.144777584</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2884435104860857</v>
+        <v>0.2960261201887759</v>
       </c>
       <c r="T69">
-        <v>1.691817938170439</v>
+        <v>1.744687248738265</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0771030854233367</v>
+        <v>0.07596921652005234</v>
       </c>
       <c r="W69">
-        <v>0.2176190924571772</v>
+        <v>0.2178864587445717</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2570102847444556</v>
+        <v>0.2532307217335078</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.242891150406717</v>
+        <v>0.244791150406717</v>
       </c>
       <c r="C70">
-        <v>-0.7497634800092812</v>
+        <v>-0.7917530139811417</v>
       </c>
       <c r="D70">
-        <v>1.276636519990719</v>
+        <v>1.264446986018858</v>
       </c>
       <c r="E70">
-        <v>2.0264</v>
+        <v>2.0562</v>
       </c>
       <c r="F70">
-        <v>2.0264</v>
+        <v>2.0562</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7149,37 +7149,37 @@
         <v>0.121</v>
       </c>
       <c r="M70">
-        <v>0.47782512</v>
+        <v>0.48485196</v>
       </c>
       <c r="N70">
-        <v>-0.3568251200000001</v>
+        <v>-0.36385196</v>
       </c>
       <c r="O70">
-        <v>-0.107047536</v>
+        <v>-0.109155588</v>
       </c>
       <c r="P70">
-        <v>-0.2497775840000001</v>
+        <v>-0.254696372</v>
       </c>
       <c r="Q70">
-        <v>-0.144777584</v>
+        <v>-0.149696372</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2960261201887759</v>
+        <v>0.3040979305174462</v>
       </c>
       <c r="T70">
-        <v>1.744687248738265</v>
+        <v>1.800967482568532</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07596921652005234</v>
+        <v>0.07486821338208058</v>
       </c>
       <c r="W70">
-        <v>0.2178864587445717</v>
+        <v>0.2181460752845054</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2532307217335078</v>
+        <v>0.2495607112736019</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.244791150406717</v>
+        <v>0.246691150406717</v>
       </c>
       <c r="C71">
-        <v>-0.7917530139811417</v>
+        <v>-0.833511974187064</v>
       </c>
       <c r="D71">
-        <v>1.264446986018858</v>
+        <v>1.252488025812936</v>
       </c>
       <c r="E71">
-        <v>2.0562</v>
+        <v>2.086</v>
       </c>
       <c r="F71">
-        <v>2.0562</v>
+        <v>2.086</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7231,37 +7231,37 @@
         <v>0.121</v>
       </c>
       <c r="M71">
-        <v>0.48485196</v>
+        <v>0.4918788000000001</v>
       </c>
       <c r="N71">
-        <v>-0.36385196</v>
+        <v>-0.3708788000000001</v>
       </c>
       <c r="O71">
-        <v>-0.109155588</v>
+        <v>-0.11126364</v>
       </c>
       <c r="P71">
-        <v>-0.254696372</v>
+        <v>-0.2596151600000001</v>
       </c>
       <c r="Q71">
-        <v>-0.149696372</v>
+        <v>-0.1546151600000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3040979305174462</v>
+        <v>0.3127078615346943</v>
       </c>
       <c r="T71">
-        <v>1.800967482568532</v>
+        <v>1.860999731987483</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07486821338208058</v>
+        <v>0.07379866747662227</v>
       </c>
       <c r="W71">
-        <v>0.2181460752845054</v>
+        <v>0.2183982742090125</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2495607112736019</v>
+        <v>0.2459955582554075</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.246691150406717</v>
+        <v>0.248591150406717</v>
       </c>
       <c r="C72">
-        <v>-0.833511974187064</v>
+        <v>-0.8750468415334538</v>
       </c>
       <c r="D72">
-        <v>1.252488025812936</v>
+        <v>1.240753158466546</v>
       </c>
       <c r="E72">
-        <v>2.086</v>
+        <v>2.1158</v>
       </c>
       <c r="F72">
-        <v>2.086</v>
+        <v>2.1158</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7313,37 +7313,37 @@
         <v>0.121</v>
       </c>
       <c r="M72">
-        <v>0.4918788000000001</v>
+        <v>0.49890564</v>
       </c>
       <c r="N72">
-        <v>-0.3708788000000001</v>
+        <v>-0.37790564</v>
       </c>
       <c r="O72">
-        <v>-0.11126364</v>
+        <v>-0.113371692</v>
       </c>
       <c r="P72">
-        <v>-0.2596151600000001</v>
+        <v>-0.264533948</v>
       </c>
       <c r="Q72">
-        <v>-0.1546151600000001</v>
+        <v>-0.159533948</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3127078615346943</v>
+        <v>0.3219115808979597</v>
       </c>
       <c r="T72">
-        <v>1.860999731987483</v>
+        <v>1.925172136538776</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07379866747662227</v>
+        <v>0.07275924962483887</v>
       </c>
       <c r="W72">
-        <v>0.2183982742090125</v>
+        <v>0.218643368938463</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2459955582554075</v>
+        <v>0.2425308320827962</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.248591150406717</v>
+        <v>0.250491150406717</v>
       </c>
       <c r="C73">
-        <v>-0.8750468415334529</v>
+        <v>-0.9163638562964376</v>
       </c>
       <c r="D73">
-        <v>1.240753158466547</v>
+        <v>1.229236143703562</v>
       </c>
       <c r="E73">
-        <v>2.1158</v>
+        <v>2.1456</v>
       </c>
       <c r="F73">
-        <v>2.1158</v>
+        <v>2.1456</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7395,37 +7395,37 @@
         <v>0.121</v>
       </c>
       <c r="M73">
-        <v>0.4989056399999999</v>
+        <v>0.50593248</v>
       </c>
       <c r="N73">
-        <v>-0.3779056399999999</v>
+        <v>-0.38493248</v>
       </c>
       <c r="O73">
-        <v>-0.113371692</v>
+        <v>-0.115479744</v>
       </c>
       <c r="P73">
-        <v>-0.264533948</v>
+        <v>-0.269452736</v>
       </c>
       <c r="Q73">
-        <v>-0.159533948</v>
+        <v>-0.164452736</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3219115808979596</v>
+        <v>0.3317727087871725</v>
       </c>
       <c r="T73">
-        <v>1.925172136538775</v>
+        <v>1.993928284272303</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07275924962483889</v>
+        <v>0.07174870449116055</v>
       </c>
       <c r="W73">
-        <v>0.218643368938463</v>
+        <v>0.2188816554809843</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2425308320827962</v>
+        <v>0.2391623483038685</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.250491150406717</v>
+        <v>0.252391150406717</v>
       </c>
       <c r="C74">
-        <v>-0.9163638562964376</v>
+        <v>-0.9574690291871386</v>
       </c>
       <c r="D74">
-        <v>1.229236143703562</v>
+        <v>1.217930970812861</v>
       </c>
       <c r="E74">
-        <v>2.1456</v>
+        <v>2.1754</v>
       </c>
       <c r="F74">
-        <v>2.1456</v>
+        <v>2.1754</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7477,37 +7477,37 @@
         <v>0.121</v>
       </c>
       <c r="M74">
-        <v>0.50593248</v>
+        <v>0.51295932</v>
       </c>
       <c r="N74">
-        <v>-0.38493248</v>
+        <v>-0.39195932</v>
       </c>
       <c r="O74">
-        <v>-0.115479744</v>
+        <v>-0.117587796</v>
       </c>
       <c r="P74">
-        <v>-0.269452736</v>
+        <v>-0.274371524</v>
       </c>
       <c r="Q74">
-        <v>-0.164452736</v>
+        <v>-0.169371524</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3317727087871725</v>
+        <v>0.3423642905941047</v>
       </c>
       <c r="T74">
-        <v>1.993928284272303</v>
+        <v>2.067777479986092</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07174870449116055</v>
+        <v>0.07076584552552821</v>
       </c>
       <c r="W74">
-        <v>0.2188816554809843</v>
+        <v>0.2191134136250805</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2391623483038685</v>
+        <v>0.2358861517517608</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.252391150406717</v>
+        <v>0.254291150406717</v>
       </c>
       <c r="C75">
-        <v>-0.9574690291871386</v>
+        <v>-0.9983681518119134</v>
       </c>
       <c r="D75">
-        <v>1.217930970812861</v>
+        <v>1.206831848188087</v>
       </c>
       <c r="E75">
-        <v>2.1754</v>
+        <v>2.2052</v>
       </c>
       <c r="F75">
-        <v>2.1754</v>
+        <v>2.2052</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7559,37 +7559,37 @@
         <v>0.121</v>
       </c>
       <c r="M75">
-        <v>0.51295932</v>
+        <v>0.5199861600000001</v>
       </c>
       <c r="N75">
-        <v>-0.39195932</v>
+        <v>-0.3989861600000001</v>
       </c>
       <c r="O75">
-        <v>-0.117587796</v>
+        <v>-0.119695848</v>
       </c>
       <c r="P75">
-        <v>-0.274371524</v>
+        <v>-0.2792903120000001</v>
       </c>
       <c r="Q75">
-        <v>-0.169371524</v>
+        <v>-0.1742903120000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3423642905941047</v>
+        <v>0.3537706094631088</v>
       </c>
       <c r="T75">
-        <v>2.067777479986092</v>
+        <v>2.14730738306248</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07076584552552821</v>
+        <v>0.06980955031572376</v>
       </c>
       <c r="W75">
-        <v>0.2191134136250805</v>
+        <v>0.2193389080355523</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2358861517517608</v>
+        <v>0.2326985010524126</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.254291150406717</v>
+        <v>0.256191150406717</v>
       </c>
       <c r="C76">
-        <v>-0.9983681518119134</v>
+        <v>-1.039066806565807</v>
       </c>
       <c r="D76">
-        <v>1.206831848188087</v>
+        <v>1.195933193434193</v>
       </c>
       <c r="E76">
-        <v>2.2052</v>
+        <v>2.235</v>
       </c>
       <c r="F76">
-        <v>2.2052</v>
+        <v>2.235</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7641,37 +7641,37 @@
         <v>0.121</v>
       </c>
       <c r="M76">
-        <v>0.5199861600000001</v>
+        <v>0.527013</v>
       </c>
       <c r="N76">
-        <v>-0.3989861600000001</v>
+        <v>-0.406013</v>
       </c>
       <c r="O76">
-        <v>-0.119695848</v>
+        <v>-0.1218039</v>
       </c>
       <c r="P76">
-        <v>-0.2792903120000001</v>
+        <v>-0.2842091</v>
       </c>
       <c r="Q76">
-        <v>-0.1742903120000001</v>
+        <v>-0.1792091</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3537706094631088</v>
+        <v>0.3660894338416331</v>
       </c>
       <c r="T76">
-        <v>2.14730738306248</v>
+        <v>2.233199678384979</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06980955031572376</v>
+        <v>0.06887875631151415</v>
       </c>
       <c r="W76">
-        <v>0.2193389080355523</v>
+        <v>0.219558389261745</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2326985010524126</v>
+        <v>0.2295958543717138</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.256191150406717</v>
+        <v>0.258091150406717</v>
       </c>
       <c r="C77">
-        <v>-1.039066806565807</v>
+        <v>-1.079570375994734</v>
       </c>
       <c r="D77">
-        <v>1.195933193434193</v>
+        <v>1.185229624005266</v>
       </c>
       <c r="E77">
-        <v>2.235</v>
+        <v>2.2648</v>
       </c>
       <c r="F77">
-        <v>2.235</v>
+        <v>2.2648</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7723,37 +7723,37 @@
         <v>0.121</v>
       </c>
       <c r="M77">
-        <v>0.527013</v>
+        <v>0.53403984</v>
       </c>
       <c r="N77">
-        <v>-0.406013</v>
+        <v>-0.41303984</v>
       </c>
       <c r="O77">
-        <v>-0.1218039</v>
+        <v>-0.123911952</v>
       </c>
       <c r="P77">
-        <v>-0.2842091</v>
+        <v>-0.2891278880000001</v>
       </c>
       <c r="Q77">
-        <v>-0.1792091</v>
+        <v>-0.184127888</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3660894338416331</v>
+        <v>0.3794348269183679</v>
       </c>
       <c r="T77">
-        <v>2.233199678384979</v>
+        <v>2.326249664984354</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06887875631151415</v>
+        <v>0.06797245688636262</v>
       </c>
       <c r="W77">
-        <v>0.219558389261745</v>
+        <v>0.2197720946661957</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2295958543717138</v>
+        <v>0.2265748562878754</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.258091150406717</v>
+        <v>0.2599911504067171</v>
       </c>
       <c r="C78">
-        <v>-1.079570375994734</v>
+        <v>-1.119884051659363</v>
       </c>
       <c r="D78">
-        <v>1.185229624005266</v>
+        <v>1.174715948340637</v>
       </c>
       <c r="E78">
-        <v>2.2648</v>
+        <v>2.2946</v>
       </c>
       <c r="F78">
-        <v>2.2648</v>
+        <v>2.2946</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7805,37 +7805,37 @@
         <v>0.121</v>
       </c>
       <c r="M78">
-        <v>0.53403984</v>
+        <v>0.54106668</v>
       </c>
       <c r="N78">
-        <v>-0.41303984</v>
+        <v>-0.42006668</v>
       </c>
       <c r="O78">
-        <v>-0.123911952</v>
+        <v>-0.126020004</v>
       </c>
       <c r="P78">
-        <v>-0.2891278880000001</v>
+        <v>-0.294046676</v>
       </c>
       <c r="Q78">
-        <v>-0.184127888</v>
+        <v>-0.189046676</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3794348269183679</v>
+        <v>0.393940688958297</v>
       </c>
       <c r="T78">
-        <v>2.326249664984354</v>
+        <v>2.427390954766282</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06797245688636262</v>
+        <v>0.06708969770602026</v>
       </c>
       <c r="W78">
-        <v>0.2197720946661957</v>
+        <v>0.2199802492809204</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2265748562878754</v>
+        <v>0.2236323256867342</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2599911504067171</v>
+        <v>0.261891150406717</v>
       </c>
       <c r="C79">
-        <v>-1.119884051659363</v>
+        <v>-1.160012842531392</v>
       </c>
       <c r="D79">
-        <v>1.174715948340637</v>
+        <v>1.164387157468608</v>
       </c>
       <c r="E79">
-        <v>2.2946</v>
+        <v>2.3244</v>
       </c>
       <c r="F79">
-        <v>2.2946</v>
+        <v>2.3244</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7887,37 +7887,37 @@
         <v>0.121</v>
       </c>
       <c r="M79">
-        <v>0.54106668</v>
+        <v>0.5480935200000001</v>
       </c>
       <c r="N79">
-        <v>-0.42006668</v>
+        <v>-0.4270935200000001</v>
       </c>
       <c r="O79">
-        <v>-0.126020004</v>
+        <v>-0.128128056</v>
       </c>
       <c r="P79">
-        <v>-0.294046676</v>
+        <v>-0.2989654640000001</v>
       </c>
       <c r="Q79">
-        <v>-0.189046676</v>
+        <v>-0.1939654640000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.393940688958297</v>
+        <v>0.4097652657291286</v>
       </c>
       <c r="T79">
-        <v>2.427390954766282</v>
+        <v>2.537726907255659</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06708969770602026</v>
+        <v>0.06622957337645588</v>
       </c>
       <c r="W79">
-        <v>0.2199802492809204</v>
+        <v>0.2201830665978317</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2236323256867342</v>
+        <v>0.2207652445881862</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.261891150406717</v>
+        <v>0.2637911504067171</v>
       </c>
       <c r="C80">
-        <v>-1.160012842531392</v>
+        <v>-1.199961582950729</v>
       </c>
       <c r="D80">
-        <v>1.164387157468608</v>
+        <v>1.154238417049271</v>
       </c>
       <c r="E80">
-        <v>2.3244</v>
+        <v>2.3542</v>
       </c>
       <c r="F80">
-        <v>2.3244</v>
+        <v>2.3542</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7969,37 +7969,37 @@
         <v>0.121</v>
       </c>
       <c r="M80">
-        <v>0.5480935200000001</v>
+        <v>0.5551203600000001</v>
       </c>
       <c r="N80">
-        <v>-0.4270935200000001</v>
+        <v>-0.4341203600000001</v>
       </c>
       <c r="O80">
-        <v>-0.128128056</v>
+        <v>-0.130236108</v>
       </c>
       <c r="P80">
-        <v>-0.2989654640000001</v>
+        <v>-0.3038842520000001</v>
       </c>
       <c r="Q80">
-        <v>-0.1939654640000001</v>
+        <v>-0.1988842520000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4097652657291286</v>
+        <v>0.4270969450495634</v>
       </c>
       <c r="T80">
-        <v>2.537726907255659</v>
+        <v>2.658571045696405</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06622957337645588</v>
+        <v>0.06539122434637416</v>
       </c>
       <c r="W80">
-        <v>0.2201830665978317</v>
+        <v>0.220380749299125</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2207652445881862</v>
+        <v>0.2179707478212473</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2637911504067171</v>
+        <v>0.265691150406717</v>
       </c>
       <c r="C81">
-        <v>-1.199961582950729</v>
+        <v>-1.239734940170141</v>
       </c>
       <c r="D81">
-        <v>1.154238417049271</v>
+        <v>1.144265059829859</v>
       </c>
       <c r="E81">
-        <v>2.3542</v>
+        <v>2.384</v>
       </c>
       <c r="F81">
-        <v>2.3542</v>
+        <v>2.384</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -8051,37 +8051,37 @@
         <v>0.121</v>
       </c>
       <c r="M81">
-        <v>0.5551203600000001</v>
+        <v>0.5621472</v>
       </c>
       <c r="N81">
-        <v>-0.4341203600000001</v>
+        <v>-0.4411472</v>
       </c>
       <c r="O81">
-        <v>-0.130236108</v>
+        <v>-0.13234416</v>
       </c>
       <c r="P81">
-        <v>-0.3038842520000001</v>
+        <v>-0.30880304</v>
       </c>
       <c r="Q81">
-        <v>-0.1988842520000001</v>
+        <v>-0.20380304</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4270969450495634</v>
+        <v>0.4461617923020416</v>
       </c>
       <c r="T81">
-        <v>2.658571045696405</v>
+        <v>2.791499597981225</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06539122434637416</v>
+        <v>0.0645738340420445</v>
       </c>
       <c r="W81">
-        <v>0.220380749299125</v>
+        <v>0.2205734899328859</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2179707478212473</v>
+        <v>0.2152461134734817</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.265691150406717</v>
+        <v>0.267591150406717</v>
       </c>
       <c r="C82">
-        <v>-1.239734940170141</v>
+        <v>-1.279337421512115</v>
       </c>
       <c r="D82">
-        <v>1.144265059829859</v>
+        <v>1.134462578487885</v>
       </c>
       <c r="E82">
-        <v>2.384</v>
+        <v>2.4138</v>
       </c>
       <c r="F82">
-        <v>2.384</v>
+        <v>2.4138</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8133,37 +8133,37 @@
         <v>0.121</v>
       </c>
       <c r="M82">
-        <v>0.5621472</v>
+        <v>0.56917404</v>
       </c>
       <c r="N82">
-        <v>-0.4411472</v>
+        <v>-0.4481740400000001</v>
       </c>
       <c r="O82">
-        <v>-0.13234416</v>
+        <v>-0.134452212</v>
       </c>
       <c r="P82">
-        <v>-0.30880304</v>
+        <v>-0.313721828</v>
       </c>
       <c r="Q82">
-        <v>-0.20380304</v>
+        <v>-0.208721828</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4461617923020416</v>
+        <v>0.4672334655810964</v>
       </c>
       <c r="T82">
-        <v>2.791499597981225</v>
+        <v>2.938420629453921</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0645738340420445</v>
+        <v>0.06377662621436493</v>
       </c>
       <c r="W82">
-        <v>0.2205734899328859</v>
+        <v>0.2207614715386527</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2152461134734817</v>
+        <v>0.2125887540478831</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.267591150406717</v>
+        <v>0.269491150406717</v>
       </c>
       <c r="C83">
-        <v>-1.279337421512115</v>
+        <v>-1.318773381160978</v>
       </c>
       <c r="D83">
-        <v>1.134462578487885</v>
+        <v>1.124826618839022</v>
       </c>
       <c r="E83">
-        <v>2.4138</v>
+        <v>2.4436</v>
       </c>
       <c r="F83">
-        <v>2.4138</v>
+        <v>2.4436</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8215,37 +8215,37 @@
         <v>0.121</v>
       </c>
       <c r="M83">
-        <v>0.56917404</v>
+        <v>0.57620088</v>
       </c>
       <c r="N83">
-        <v>-0.4481740400000001</v>
+        <v>-0.45520088</v>
       </c>
       <c r="O83">
-        <v>-0.134452212</v>
+        <v>-0.136560264</v>
       </c>
       <c r="P83">
-        <v>-0.313721828</v>
+        <v>-0.318640616</v>
       </c>
       <c r="Q83">
-        <v>-0.208721828</v>
+        <v>-0.213640616</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4672334655810964</v>
+        <v>0.4906464358911573</v>
       </c>
       <c r="T83">
-        <v>2.938420629453921</v>
+        <v>3.101666219979139</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06377662621436493</v>
+        <v>0.06299886248004341</v>
       </c>
       <c r="W83">
-        <v>0.2207614715386527</v>
+        <v>0.2209448682272058</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2125887540478831</v>
+        <v>0.2099962082668114</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.269491150406717</v>
+        <v>0.271391150406717</v>
       </c>
       <c r="C84">
-        <v>-1.318773381160978</v>
+        <v>-1.358047026611791</v>
       </c>
       <c r="D84">
-        <v>1.124826618839022</v>
+        <v>1.11535297338821</v>
       </c>
       <c r="E84">
-        <v>2.4436</v>
+        <v>2.4734</v>
       </c>
       <c r="F84">
-        <v>2.4436</v>
+        <v>2.4734</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8297,37 +8297,37 @@
         <v>0.121</v>
       </c>
       <c r="M84">
-        <v>0.57620088</v>
+        <v>0.5832277200000001</v>
       </c>
       <c r="N84">
-        <v>-0.45520088</v>
+        <v>-0.4622277200000001</v>
       </c>
       <c r="O84">
-        <v>-0.136560264</v>
+        <v>-0.138668316</v>
       </c>
       <c r="P84">
-        <v>-0.318640616</v>
+        <v>-0.3235594040000001</v>
       </c>
       <c r="Q84">
-        <v>-0.213640616</v>
+        <v>-0.218559404</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4906464358911573</v>
+        <v>0.5168138732965195</v>
       </c>
       <c r="T84">
-        <v>3.101666219979139</v>
+        <v>3.284117174095559</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06299886248004341</v>
+        <v>0.0622398400405248</v>
       </c>
       <c r="W84">
-        <v>0.2209448682272058</v>
+        <v>0.2211238457184443</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2099962082668114</v>
+        <v>0.207466133468416</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.271391150406717</v>
+        <v>0.273291150406717</v>
       </c>
       <c r="C85">
-        <v>-1.358047026611791</v>
+        <v>-1.397162424796067</v>
       </c>
       <c r="D85">
-        <v>1.11535297338821</v>
+        <v>1.106037575203933</v>
       </c>
       <c r="E85">
-        <v>2.4734</v>
+        <v>2.5032</v>
       </c>
       <c r="F85">
-        <v>2.4734</v>
+        <v>2.5032</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8379,37 +8379,37 @@
         <v>0.121</v>
       </c>
       <c r="M85">
-        <v>0.5832277200000001</v>
+        <v>0.5902545600000001</v>
       </c>
       <c r="N85">
-        <v>-0.4622277200000001</v>
+        <v>-0.4692545600000001</v>
       </c>
       <c r="O85">
-        <v>-0.138668316</v>
+        <v>-0.140776368</v>
       </c>
       <c r="P85">
-        <v>-0.3235594040000001</v>
+        <v>-0.3284781920000001</v>
       </c>
       <c r="Q85">
-        <v>-0.218559404</v>
+        <v>-0.223478192</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5168138732965195</v>
+        <v>0.546252240377552</v>
       </c>
       <c r="T85">
-        <v>3.284117174095559</v>
+        <v>3.489374497476533</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0622398400405248</v>
+        <v>0.0614988895638519</v>
       </c>
       <c r="W85">
-        <v>0.2211238457184443</v>
+        <v>0.2212985618408437</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.207466133468416</v>
+        <v>0.204996298546173</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.273291150406717</v>
+        <v>0.275191150406717</v>
       </c>
       <c r="C86">
-        <v>-1.397162424796067</v>
+        <v>-1.436123507903072</v>
       </c>
       <c r="D86">
-        <v>1.106037575203933</v>
+        <v>1.096876492096928</v>
       </c>
       <c r="E86">
-        <v>2.5032</v>
+        <v>2.533</v>
       </c>
       <c r="F86">
-        <v>2.5032</v>
+        <v>2.533</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8461,37 +8461,37 @@
         <v>0.121</v>
       </c>
       <c r="M86">
-        <v>0.5902545600000001</v>
+        <v>0.5972814</v>
       </c>
       <c r="N86">
-        <v>-0.4692545600000001</v>
+        <v>-0.4762814</v>
       </c>
       <c r="O86">
-        <v>-0.140776368</v>
+        <v>-0.14288442</v>
       </c>
       <c r="P86">
-        <v>-0.3284781920000001</v>
+        <v>-0.33339698</v>
       </c>
       <c r="Q86">
-        <v>-0.223478192</v>
+        <v>-0.2283969799999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5462522403775517</v>
+        <v>0.5796157230693885</v>
       </c>
       <c r="T86">
-        <v>3.48937449747653</v>
+        <v>3.721999463974965</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0614988895638519</v>
+        <v>0.06077537321604189</v>
       </c>
       <c r="W86">
-        <v>0.2212985618408437</v>
+        <v>0.2214691669956573</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.204996298546173</v>
+        <v>0.2025845773868062</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.275191150406717</v>
+        <v>0.277091150406717</v>
       </c>
       <c r="C87">
-        <v>-1.436123507903072</v>
+        <v>-1.474934078914195</v>
       </c>
       <c r="D87">
-        <v>1.096876492096928</v>
+        <v>1.087865921085805</v>
       </c>
       <c r="E87">
-        <v>2.533</v>
+        <v>2.5628</v>
       </c>
       <c r="F87">
-        <v>2.533</v>
+        <v>2.5628</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8543,37 +8543,37 @@
         <v>0.121</v>
       </c>
       <c r="M87">
-        <v>0.5972814</v>
+        <v>0.6043082399999999</v>
       </c>
       <c r="N87">
-        <v>-0.4762814</v>
+        <v>-0.4833082399999999</v>
       </c>
       <c r="O87">
-        <v>-0.14288442</v>
+        <v>-0.144992472</v>
       </c>
       <c r="P87">
-        <v>-0.33339698</v>
+        <v>-0.338315768</v>
       </c>
       <c r="Q87">
-        <v>-0.2283969799999999</v>
+        <v>-0.233315768</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5796157230693885</v>
+        <v>0.6177454175743449</v>
       </c>
       <c r="T87">
-        <v>3.721999463974965</v>
+        <v>3.987856568544606</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06077537321604189</v>
+        <v>0.06006868282980884</v>
       </c>
       <c r="W87">
-        <v>0.2214691669956573</v>
+        <v>0.2216358045887311</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2025845773868062</v>
+        <v>0.2002289427660294</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.277091150406717</v>
+        <v>0.278991150406717</v>
       </c>
       <c r="C88">
-        <v>-1.474934078914195</v>
+        <v>-1.513597816866763</v>
       </c>
       <c r="D88">
-        <v>1.087865921085805</v>
+        <v>1.079002183133237</v>
       </c>
       <c r="E88">
-        <v>2.5628</v>
+        <v>2.5926</v>
       </c>
       <c r="F88">
-        <v>2.5628</v>
+        <v>2.5926</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8625,37 +8625,37 @@
         <v>0.121</v>
       </c>
       <c r="M88">
-        <v>0.6043082399999999</v>
+        <v>0.61133508</v>
       </c>
       <c r="N88">
-        <v>-0.4833082399999999</v>
+        <v>-0.49033508</v>
       </c>
       <c r="O88">
-        <v>-0.144992472</v>
+        <v>-0.147100524</v>
       </c>
       <c r="P88">
-        <v>-0.338315768</v>
+        <v>-0.343234556</v>
       </c>
       <c r="Q88">
-        <v>-0.233315768</v>
+        <v>-0.238234556</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6177454175743449</v>
+        <v>0.6617412189262175</v>
       </c>
       <c r="T88">
-        <v>3.987856568544606</v>
+        <v>4.29461476612496</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06006868282980884</v>
+        <v>0.05937823819958115</v>
       </c>
       <c r="W88">
-        <v>0.2216358045887311</v>
+        <v>0.2217986114325388</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2002289427660294</v>
+        <v>0.1979274606652704</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.278991150406717</v>
+        <v>0.280891150406717</v>
       </c>
       <c r="C89">
-        <v>-1.513597816866763</v>
+        <v>-1.552118281862601</v>
       </c>
       <c r="D89">
-        <v>1.079002183133237</v>
+        <v>1.070281718137398</v>
       </c>
       <c r="E89">
-        <v>2.5926</v>
+        <v>2.6224</v>
       </c>
       <c r="F89">
-        <v>2.5926</v>
+        <v>2.6224</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8707,37 +8707,37 @@
         <v>0.121</v>
       </c>
       <c r="M89">
-        <v>0.61133508</v>
+        <v>0.61836192</v>
       </c>
       <c r="N89">
-        <v>-0.49033508</v>
+        <v>-0.49736192</v>
       </c>
       <c r="O89">
-        <v>-0.147100524</v>
+        <v>-0.149208576</v>
       </c>
       <c r="P89">
-        <v>-0.343234556</v>
+        <v>-0.348153344</v>
       </c>
       <c r="Q89">
-        <v>-0.238234556</v>
+        <v>-0.243153344</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6617412189262175</v>
+        <v>0.7130696538367357</v>
       </c>
       <c r="T89">
-        <v>4.29461476612496</v>
+        <v>4.652499329968707</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05937823819958115</v>
+        <v>0.05870348549276773</v>
       </c>
       <c r="W89">
-        <v>0.2217986114325388</v>
+        <v>0.2219577181208054</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1979274606652704</v>
+        <v>0.1956782849758925</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.280891150406717</v>
+        <v>0.282791150406717</v>
       </c>
       <c r="C90">
-        <v>-1.552118281862601</v>
+        <v>-1.59049891983567</v>
       </c>
       <c r="D90">
-        <v>1.070281718137398</v>
+        <v>1.06170108016433</v>
       </c>
       <c r="E90">
-        <v>2.6224</v>
+        <v>2.6522</v>
       </c>
       <c r="F90">
-        <v>2.6224</v>
+        <v>2.6522</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8789,37 +8789,37 @@
         <v>0.121</v>
       </c>
       <c r="M90">
-        <v>0.61836192</v>
+        <v>0.6253887600000001</v>
       </c>
       <c r="N90">
-        <v>-0.49736192</v>
+        <v>-0.5043887600000001</v>
       </c>
       <c r="O90">
-        <v>-0.149208576</v>
+        <v>-0.151316628</v>
       </c>
       <c r="P90">
-        <v>-0.348153344</v>
+        <v>-0.3530721320000001</v>
       </c>
       <c r="Q90">
-        <v>-0.243153344</v>
+        <v>-0.2480721320000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7130696538367357</v>
+        <v>0.7737305314582572</v>
       </c>
       <c r="T90">
-        <v>4.652499329968707</v>
+        <v>5.075453814511317</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05870348549276773</v>
+        <v>0.05804389576812988</v>
       </c>
       <c r="W90">
-        <v>0.2219577181208054</v>
+        <v>0.222113249377875</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1956782849758925</v>
+        <v>0.193479652560433</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.282791150406717</v>
+        <v>0.2846911504067171</v>
       </c>
       <c r="C91">
-        <v>-1.59049891983567</v>
+        <v>-1.628743067092183</v>
       </c>
       <c r="D91">
-        <v>1.06170108016433</v>
+        <v>1.053256932907817</v>
       </c>
       <c r="E91">
-        <v>2.6522</v>
+        <v>2.682</v>
       </c>
       <c r="F91">
-        <v>2.6522</v>
+        <v>2.682</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8871,37 +8871,37 @@
         <v>0.121</v>
       </c>
       <c r="M91">
-        <v>0.6253887600000001</v>
+        <v>0.6324156</v>
       </c>
       <c r="N91">
-        <v>-0.5043887600000001</v>
+        <v>-0.5114156</v>
       </c>
       <c r="O91">
-        <v>-0.151316628</v>
+        <v>-0.15342468</v>
       </c>
       <c r="P91">
-        <v>-0.3530721320000001</v>
+        <v>-0.35799092</v>
       </c>
       <c r="Q91">
-        <v>-0.2480721320000001</v>
+        <v>-0.25299092</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7737305314582572</v>
+        <v>0.8465235846040831</v>
       </c>
       <c r="T91">
-        <v>5.075453814511317</v>
+        <v>5.58299919596245</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05804389576812988</v>
+        <v>0.05739896359292845</v>
       </c>
       <c r="W91">
-        <v>0.222113249377875</v>
+        <v>0.2222653243847875</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.193479652560433</v>
+        <v>0.1913298786430948</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2846911504067171</v>
+        <v>0.286591150406717</v>
       </c>
       <c r="C92">
-        <v>-1.628743067092183</v>
+        <v>-1.666853954635786</v>
       </c>
       <c r="D92">
-        <v>1.053256932907817</v>
+        <v>1.044946045364214</v>
       </c>
       <c r="E92">
-        <v>2.682</v>
+        <v>2.7118</v>
       </c>
       <c r="F92">
-        <v>2.682</v>
+        <v>2.7118</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8953,37 +8953,37 @@
         <v>0.121</v>
       </c>
       <c r="M92">
-        <v>0.6324156</v>
+        <v>0.6394424400000001</v>
       </c>
       <c r="N92">
-        <v>-0.5114156</v>
+        <v>-0.5184424400000001</v>
       </c>
       <c r="O92">
-        <v>-0.15342468</v>
+        <v>-0.155532732</v>
       </c>
       <c r="P92">
-        <v>-0.35799092</v>
+        <v>-0.3629097080000001</v>
       </c>
       <c r="Q92">
-        <v>-0.25299092</v>
+        <v>-0.257909708</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8465235846040831</v>
+        <v>0.9354928717823146</v>
       </c>
       <c r="T92">
-        <v>5.58299919596245</v>
+        <v>6.203332439958278</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05739896359292845</v>
+        <v>0.05676820575124791</v>
       </c>
       <c r="W92">
-        <v>0.2222653243847875</v>
+        <v>0.2224140570838558</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1913298786430948</v>
+        <v>0.1892273525041597</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.286591150406717</v>
+        <v>0.2884911504067171</v>
       </c>
       <c r="C93">
-        <v>-1.666853954635786</v>
+        <v>-1.704834712289556</v>
       </c>
       <c r="D93">
-        <v>1.044946045364214</v>
+        <v>1.036765287710444</v>
       </c>
       <c r="E93">
-        <v>2.7118</v>
+        <v>2.7416</v>
       </c>
       <c r="F93">
-        <v>2.7118</v>
+        <v>2.7416</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -9035,37 +9035,37 @@
         <v>0.121</v>
       </c>
       <c r="M93">
-        <v>0.6394424400000001</v>
+        <v>0.64646928</v>
       </c>
       <c r="N93">
-        <v>-0.5184424400000001</v>
+        <v>-0.52546928</v>
       </c>
       <c r="O93">
-        <v>-0.155532732</v>
+        <v>-0.157640784</v>
       </c>
       <c r="P93">
-        <v>-0.3629097080000001</v>
+        <v>-0.367828496</v>
       </c>
       <c r="Q93">
-        <v>-0.257909708</v>
+        <v>-0.262828496</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9354928717823146</v>
+        <v>1.046704480755104</v>
       </c>
       <c r="T93">
-        <v>6.203332439958278</v>
+        <v>6.978748994953065</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05676820575124791</v>
+        <v>0.05615116003656043</v>
       </c>
       <c r="W93">
-        <v>0.2224140570838558</v>
+        <v>0.2225595564633791</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1892273525041597</v>
+        <v>0.1871705334552014</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2884911504067171</v>
+        <v>0.290391150406717</v>
       </c>
       <c r="C94">
-        <v>-1.704834712289556</v>
+        <v>-1.742688372625894</v>
       </c>
       <c r="D94">
-        <v>1.036765287710444</v>
+        <v>1.028711627374106</v>
       </c>
       <c r="E94">
-        <v>2.7416</v>
+        <v>2.7714</v>
       </c>
       <c r="F94">
-        <v>2.7416</v>
+        <v>2.7714</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -9117,37 +9117,37 @@
         <v>0.121</v>
       </c>
       <c r="M94">
-        <v>0.64646928</v>
+        <v>0.6534961200000001</v>
       </c>
       <c r="N94">
-        <v>-0.52546928</v>
+        <v>-0.5324961200000001</v>
       </c>
       <c r="O94">
-        <v>-0.157640784</v>
+        <v>-0.159748836</v>
       </c>
       <c r="P94">
-        <v>-0.367828496</v>
+        <v>-0.3727472840000001</v>
       </c>
       <c r="Q94">
-        <v>-0.262828496</v>
+        <v>-0.2677472840000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.046704480755104</v>
+        <v>1.189690835148691</v>
       </c>
       <c r="T94">
-        <v>6.978748994953065</v>
+        <v>7.975713137089217</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05615116003656043</v>
+        <v>0.05554738412218881</v>
       </c>
       <c r="W94">
-        <v>0.2225595564633791</v>
+        <v>0.2227019268239879</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1871705334552014</v>
+        <v>0.1851579470739627</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.290391150406717</v>
+        <v>0.292291150406717</v>
       </c>
       <c r="C95">
-        <v>-1.742688372625894</v>
+        <v>-1.780417874714654</v>
       </c>
       <c r="D95">
-        <v>1.028711627374106</v>
+        <v>1.020782125285347</v>
       </c>
       <c r="E95">
-        <v>2.7714</v>
+        <v>2.8012</v>
       </c>
       <c r="F95">
-        <v>2.7714</v>
+        <v>2.8012</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9199,37 +9199,37 @@
         <v>0.121</v>
       </c>
       <c r="M95">
-        <v>0.6534961200000001</v>
+        <v>0.6605229600000001</v>
       </c>
       <c r="N95">
-        <v>-0.5324961200000001</v>
+        <v>-0.5395229600000001</v>
       </c>
       <c r="O95">
-        <v>-0.159748836</v>
+        <v>-0.161856888</v>
       </c>
       <c r="P95">
-        <v>-0.3727472840000001</v>
+        <v>-0.3776660720000001</v>
       </c>
       <c r="Q95">
-        <v>-0.2677472840000001</v>
+        <v>-0.272666072</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.189690835148691</v>
+        <v>1.380339307673473</v>
       </c>
       <c r="T95">
-        <v>7.975713137089217</v>
+        <v>9.304998659937423</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05554738412218881</v>
+        <v>0.05495645450386765</v>
       </c>
       <c r="W95">
-        <v>0.2227019268239879</v>
+        <v>0.222841268027988</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1851579470739627</v>
+        <v>0.1831881816795589</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.292291150406717</v>
+        <v>0.2941911504067171</v>
       </c>
       <c r="C96">
-        <v>-1.780417874714654</v>
+        <v>-1.818026067699252</v>
       </c>
       <c r="D96">
-        <v>1.020782125285347</v>
+        <v>1.012973932300748</v>
       </c>
       <c r="E96">
-        <v>2.8012</v>
+        <v>2.831</v>
       </c>
       <c r="F96">
-        <v>2.8012</v>
+        <v>2.831</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9281,37 +9281,37 @@
         <v>0.121</v>
       </c>
       <c r="M96">
-        <v>0.6605229600000001</v>
+        <v>0.6675498</v>
       </c>
       <c r="N96">
-        <v>-0.5395229600000001</v>
+        <v>-0.5465498</v>
       </c>
       <c r="O96">
-        <v>-0.161856888</v>
+        <v>-0.16396494</v>
       </c>
       <c r="P96">
-        <v>-0.3776660720000001</v>
+        <v>-0.38258486</v>
       </c>
       <c r="Q96">
-        <v>-0.272666072</v>
+        <v>-0.27758486</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.380339307673473</v>
+        <v>1.647247169208168</v>
       </c>
       <c r="T96">
-        <v>9.304998659937423</v>
+        <v>11.16599839192491</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05495645450386765</v>
+        <v>0.0543779655090901</v>
       </c>
       <c r="W96">
-        <v>0.222841268027988</v>
+        <v>0.2229776757329565</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1831881816795589</v>
+        <v>0.1812598850303003</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2941911504067171</v>
+        <v>0.296091150406717</v>
       </c>
       <c r="C97">
-        <v>-1.818026067699252</v>
+        <v>-1.855515714209902</v>
       </c>
       <c r="D97">
-        <v>1.012973932300748</v>
+        <v>1.005284285790099</v>
       </c>
       <c r="E97">
-        <v>2.831</v>
+        <v>2.8608</v>
       </c>
       <c r="F97">
-        <v>2.831</v>
+        <v>2.8608</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9363,37 +9363,37 @@
         <v>0.121</v>
       </c>
       <c r="M97">
-        <v>0.6675498</v>
+        <v>0.6745766400000001</v>
       </c>
       <c r="N97">
-        <v>-0.5465498</v>
+        <v>-0.5535766400000001</v>
       </c>
       <c r="O97">
-        <v>-0.16396494</v>
+        <v>-0.166072992</v>
       </c>
       <c r="P97">
-        <v>-0.38258486</v>
+        <v>-0.387503648</v>
       </c>
       <c r="Q97">
-        <v>-0.27758486</v>
+        <v>-0.2825036480000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.647247169208168</v>
+        <v>2.04760896151021</v>
       </c>
       <c r="T97">
-        <v>11.16599839192491</v>
+        <v>13.95749798990615</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0543779655090901</v>
+        <v>0.05381152836837041</v>
       </c>
       <c r="W97">
-        <v>0.2229776757329565</v>
+        <v>0.2231112416107383</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1812598850303003</v>
+        <v>0.1793717612279013</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.296091150406717</v>
+        <v>0.297991150406717</v>
       </c>
       <c r="C98">
-        <v>-1.855515714209901</v>
+        <v>-1.892889493622544</v>
       </c>
       <c r="D98">
-        <v>1.005284285790099</v>
+        <v>0.9977105063774557</v>
       </c>
       <c r="E98">
-        <v>2.8608</v>
+        <v>2.8906</v>
       </c>
       <c r="F98">
-        <v>2.8608</v>
+        <v>2.8906</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9445,37 +9445,37 @@
         <v>0.121</v>
       </c>
       <c r="M98">
-        <v>0.6745766399999999</v>
+        <v>0.68160348</v>
       </c>
       <c r="N98">
-        <v>-0.55357664</v>
+        <v>-0.56060348</v>
       </c>
       <c r="O98">
-        <v>-0.166072992</v>
+        <v>-0.168181044</v>
       </c>
       <c r="P98">
-        <v>-0.387503648</v>
+        <v>-0.392422436</v>
       </c>
       <c r="Q98">
-        <v>-0.2825036479999999</v>
+        <v>-0.2874224360000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.047608961510205</v>
+        <v>2.714878615346941</v>
       </c>
       <c r="T98">
-        <v>13.95749798990611</v>
+        <v>18.60999731987481</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05381152836837042</v>
+        <v>0.05325677034395422</v>
       </c>
       <c r="W98">
-        <v>0.2231112416107383</v>
+        <v>0.2232420535528956</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1793717612279014</v>
+        <v>0.1775225678131808</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.297991150406717</v>
+        <v>0.299891150406717</v>
       </c>
       <c r="C99">
-        <v>-1.892889493622544</v>
+        <v>-1.930150005171581</v>
       </c>
       <c r="D99">
-        <v>0.9977105063774557</v>
+        <v>0.9902499948284192</v>
       </c>
       <c r="E99">
-        <v>2.8906</v>
+        <v>2.9204</v>
       </c>
       <c r="F99">
-        <v>2.8906</v>
+        <v>2.9204</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9527,37 +9527,37 @@
         <v>0.121</v>
       </c>
       <c r="M99">
-        <v>0.68160348</v>
+        <v>0.68863032</v>
       </c>
       <c r="N99">
-        <v>-0.56060348</v>
+        <v>-0.56763032</v>
       </c>
       <c r="O99">
-        <v>-0.168181044</v>
+        <v>-0.170289096</v>
       </c>
       <c r="P99">
-        <v>-0.392422436</v>
+        <v>-0.397341224</v>
       </c>
       <c r="Q99">
-        <v>-0.2874224360000001</v>
+        <v>-0.2923412240000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.714878615346941</v>
+        <v>4.049417923020411</v>
       </c>
       <c r="T99">
-        <v>18.60999731987481</v>
+        <v>27.91499597981222</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05325677034395422</v>
+        <v>0.05271333391187306</v>
       </c>
       <c r="W99">
-        <v>0.2232420535528956</v>
+        <v>0.2233701958635803</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1775225678131808</v>
+        <v>0.1757111130395769</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.299891150406717</v>
+        <v>0.301791150406717</v>
       </c>
       <c r="C100">
-        <v>-1.930150005171581</v>
+        <v>-1.96729977092397</v>
       </c>
       <c r="D100">
-        <v>0.9902499948284192</v>
+        <v>0.9829002290760301</v>
       </c>
       <c r="E100">
-        <v>2.9204</v>
+        <v>2.9502</v>
       </c>
       <c r="F100">
-        <v>2.9204</v>
+        <v>2.9502</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9609,37 +9609,37 @@
         <v>0.121</v>
       </c>
       <c r="M100">
-        <v>0.68863032</v>
+        <v>0.6956571600000001</v>
       </c>
       <c r="N100">
-        <v>-0.56763032</v>
+        <v>-0.5746571600000001</v>
       </c>
       <c r="O100">
-        <v>-0.170289096</v>
+        <v>-0.172397148</v>
       </c>
       <c r="P100">
-        <v>-0.397341224</v>
+        <v>-0.4022600120000001</v>
       </c>
       <c r="Q100">
-        <v>-0.2923412240000001</v>
+        <v>-0.2972600120000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.049417923020411</v>
+        <v>8.053035846040821</v>
       </c>
       <c r="T100">
-        <v>27.91499597981222</v>
+        <v>55.82999195962444</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05271333391187306</v>
+        <v>0.0521808759935713</v>
       </c>
       <c r="W100">
-        <v>0.2233701958635803</v>
+        <v>0.2234957494407159</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1757111130395769</v>
+        <v>0.1739362533119043</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.301791150406717</v>
-      </c>
-      <c r="C101">
-        <v>-1.96729977092397</v>
-      </c>
-      <c r="D101">
-        <v>0.9829002290760301</v>
-      </c>
-      <c r="E101">
-        <v>2.9502</v>
-      </c>
-      <c r="F101">
-        <v>2.9502</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>2.98</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.226</v>
-      </c>
-      <c r="K101">
-        <v>0.105</v>
-      </c>
-      <c r="L101">
-        <v>0.121</v>
-      </c>
-      <c r="M101">
-        <v>0.6956571600000001</v>
-      </c>
-      <c r="N101">
-        <v>-0.5746571600000001</v>
-      </c>
-      <c r="O101">
-        <v>-0.172397148</v>
-      </c>
-      <c r="P101">
-        <v>-0.4022600120000001</v>
-      </c>
-      <c r="Q101">
-        <v>-0.2972600120000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.053035846040821</v>
-      </c>
-      <c r="T101">
-        <v>55.82999195962444</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0521808759935713</v>
-      </c>
-      <c r="W101">
-        <v>0.2234957494407159</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1739362533119043</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
